--- a/research/traditional_assets/database/data/philippines/philippines_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_electrical_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1214586053756453</v>
+        <v>0.1211887088622062</v>
       </c>
       <c r="C2">
-        <v>304.3653985399526</v>
+        <v>301.5536529743586</v>
       </c>
       <c r="D2">
-        <v>243.7653985399526</v>
+        <v>244.0026529743585</v>
       </c>
       <c r="E2">
-        <v>-15.8</v>
+        <v>-12.751</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.049</v>
       </c>
       <c r="G2">
         <v>60.6</v>
@@ -1451,28 +1451,28 @@
         <v>113.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1533647</v>
       </c>
       <c r="N2">
-        <v>113.8</v>
+        <v>113.6466353</v>
       </c>
       <c r="O2">
-        <v>28.45</v>
+        <v>28.411658825</v>
       </c>
       <c r="P2">
-        <v>85.34999999999999</v>
+        <v>85.234976475</v>
       </c>
       <c r="Q2">
-        <v>92.64999999999999</v>
+        <v>92.53497647499999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1214586053756453</v>
+        <v>0.1220317766284911</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.109265235539342</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>742.0221211269607</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1211887088622062</v>
+        <v>0.1209188123487671</v>
       </c>
       <c r="C3">
-        <v>301.5536529743586</v>
+        <v>298.7423696934572</v>
       </c>
       <c r="D3">
-        <v>244.0026529743585</v>
+        <v>244.2403696934573</v>
       </c>
       <c r="E3">
-        <v>-12.751</v>
+        <v>-9.702</v>
       </c>
       <c r="F3">
-        <v>3.049</v>
+        <v>6.098000000000001</v>
       </c>
       <c r="G3">
         <v>60.6</v>
@@ -1533,28 +1533,28 @@
         <v>113.8</v>
       </c>
       <c r="M3">
-        <v>0.1533647</v>
+        <v>0.3067294</v>
       </c>
       <c r="N3">
-        <v>113.6466353</v>
+        <v>113.4932706</v>
       </c>
       <c r="O3">
-        <v>28.411658825</v>
+        <v>28.37331765</v>
       </c>
       <c r="P3">
-        <v>85.234976475</v>
+        <v>85.11995295</v>
       </c>
       <c r="Q3">
-        <v>92.53497647499999</v>
+        <v>92.41995295</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1220317766284911</v>
+        <v>0.122616645253844</v>
       </c>
       <c r="T3">
-        <v>1.109265235539342</v>
+        <v>1.117775786678971</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>742.0221211269607</v>
+        <v>371.0110605634803</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1209188123487671</v>
+        <v>0.120648915835328</v>
       </c>
       <c r="C4">
-        <v>298.7423696934572</v>
+        <v>295.9315500496928</v>
       </c>
       <c r="D4">
-        <v>244.2403696934573</v>
+        <v>244.4785500496928</v>
       </c>
       <c r="E4">
-        <v>-9.702</v>
+        <v>-6.653</v>
       </c>
       <c r="F4">
-        <v>6.098000000000001</v>
+        <v>9.147</v>
       </c>
       <c r="G4">
         <v>60.6</v>
@@ -1615,28 +1615,28 @@
         <v>113.8</v>
       </c>
       <c r="M4">
-        <v>0.3067294</v>
+        <v>0.4600941</v>
       </c>
       <c r="N4">
-        <v>113.4932706</v>
+        <v>113.3399059</v>
       </c>
       <c r="O4">
-        <v>28.37331765</v>
+        <v>28.334976475</v>
       </c>
       <c r="P4">
-        <v>85.11995295</v>
+        <v>85.004929425</v>
       </c>
       <c r="Q4">
-        <v>92.41995295</v>
+        <v>92.304929425</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.122616645253844</v>
+        <v>0.1232135730261113</v>
       </c>
       <c r="T4">
-        <v>1.117775786678971</v>
+        <v>1.126461813099831</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>371.0110605634803</v>
+        <v>247.3407070423202</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.120648915835328</v>
+        <v>0.1203790193218889</v>
       </c>
       <c r="C5">
-        <v>295.9315500496928</v>
+        <v>293.1211954007896</v>
       </c>
       <c r="D5">
-        <v>244.4785500496928</v>
+        <v>244.7171954007896</v>
       </c>
       <c r="E5">
-        <v>-6.653</v>
+        <v>-3.603999999999999</v>
       </c>
       <c r="F5">
-        <v>9.147</v>
+        <v>12.196</v>
       </c>
       <c r="G5">
         <v>60.6</v>
@@ -1697,28 +1697,28 @@
         <v>113.8</v>
       </c>
       <c r="M5">
-        <v>0.4600941</v>
+        <v>0.6134588000000001</v>
       </c>
       <c r="N5">
-        <v>113.3399059</v>
+        <v>113.1865412</v>
       </c>
       <c r="O5">
-        <v>28.334976475</v>
+        <v>28.2966353</v>
       </c>
       <c r="P5">
-        <v>85.004929425</v>
+        <v>84.8899059</v>
       </c>
       <c r="Q5">
-        <v>92.304929425</v>
+        <v>92.1899059</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1232135730261113</v>
+        <v>0.1238229367936342</v>
       </c>
       <c r="T5">
-        <v>1.126461813099831</v>
+        <v>1.135328798404458</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>247.3407070423202</v>
+        <v>185.5055302817402</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1203790193218889</v>
+        <v>0.1201091228084498</v>
       </c>
       <c r="C6">
-        <v>293.1211954007896</v>
+        <v>290.3113071097787</v>
       </c>
       <c r="D6">
-        <v>244.7171954007896</v>
+        <v>244.9563071097787</v>
       </c>
       <c r="E6">
-        <v>-3.603999999999999</v>
+        <v>-0.5549999999999979</v>
       </c>
       <c r="F6">
-        <v>12.196</v>
+        <v>15.245</v>
       </c>
       <c r="G6">
         <v>60.6</v>
@@ -1779,28 +1779,28 @@
         <v>113.8</v>
       </c>
       <c r="M6">
-        <v>0.6134588000000001</v>
+        <v>0.7668235000000001</v>
       </c>
       <c r="N6">
-        <v>113.1865412</v>
+        <v>113.0331765</v>
       </c>
       <c r="O6">
-        <v>28.2966353</v>
+        <v>28.258294125</v>
       </c>
       <c r="P6">
-        <v>84.8899059</v>
+        <v>84.774882375</v>
       </c>
       <c r="Q6">
-        <v>92.1899059</v>
+        <v>92.074882375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1238229367936342</v>
+        <v>0.1244451292720524</v>
       </c>
       <c r="T6">
-        <v>1.135328798404458</v>
+        <v>1.144382457083919</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>185.5055302817402</v>
+        <v>148.4044242253921</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1201091228084498</v>
+        <v>0.1198392262950106</v>
       </c>
       <c r="C7">
-        <v>290.3113071097787</v>
+        <v>287.501886545024</v>
       </c>
       <c r="D7">
-        <v>244.9563071097787</v>
+        <v>245.1958865450239</v>
       </c>
       <c r="E7">
-        <v>-0.5549999999999979</v>
+        <v>2.494000000000003</v>
       </c>
       <c r="F7">
-        <v>15.245</v>
+        <v>18.294</v>
       </c>
       <c r="G7">
         <v>60.6</v>
@@ -1861,28 +1861,28 @@
         <v>113.8</v>
       </c>
       <c r="M7">
-        <v>0.7668235000000001</v>
+        <v>0.9201882000000001</v>
       </c>
       <c r="N7">
-        <v>113.0331765</v>
+        <v>112.8798118</v>
       </c>
       <c r="O7">
-        <v>28.258294125</v>
+        <v>28.21995295</v>
       </c>
       <c r="P7">
-        <v>84.774882375</v>
+        <v>84.65985885000001</v>
       </c>
       <c r="Q7">
-        <v>92.074882375</v>
+        <v>91.95985885</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1244451292720524</v>
+        <v>0.1250805598883092</v>
       </c>
       <c r="T7">
-        <v>1.144382457083919</v>
+        <v>1.153628746799114</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>148.4044242253921</v>
+        <v>123.6703535211601</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1198392262950106</v>
+        <v>0.1195693297815715</v>
       </c>
       <c r="C8">
-        <v>287.501886545024</v>
+        <v>284.6929350802472</v>
       </c>
       <c r="D8">
-        <v>245.1958865450239</v>
+        <v>245.4359350802472</v>
       </c>
       <c r="E8">
-        <v>2.494</v>
+        <v>5.542999999999999</v>
       </c>
       <c r="F8">
-        <v>18.294</v>
+        <v>21.343</v>
       </c>
       <c r="G8">
         <v>60.6</v>
@@ -1943,28 +1943,28 @@
         <v>113.8</v>
       </c>
       <c r="M8">
-        <v>0.9201882</v>
+        <v>1.0735529</v>
       </c>
       <c r="N8">
-        <v>112.8798118</v>
+        <v>112.7264471</v>
       </c>
       <c r="O8">
-        <v>28.21995295</v>
+        <v>28.181611775</v>
       </c>
       <c r="P8">
-        <v>84.65985885000001</v>
+        <v>84.54483532500001</v>
       </c>
       <c r="Q8">
-        <v>91.95985885</v>
+        <v>91.84483532500001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1250805598883092</v>
+        <v>0.1257296556791092</v>
       </c>
       <c r="T8">
-        <v>1.153628746799114</v>
+        <v>1.16307388145442</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>123.6703535211601</v>
+        <v>106.0031601609944</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1195693297815715</v>
+        <v>0.1192994332681324</v>
       </c>
       <c r="C9">
-        <v>284.6929350802472</v>
+        <v>281.8844540945554</v>
       </c>
       <c r="D9">
-        <v>245.4359350802472</v>
+        <v>245.6764540945554</v>
       </c>
       <c r="E9">
-        <v>5.543000000000003</v>
+        <v>8.592000000000002</v>
       </c>
       <c r="F9">
-        <v>21.343</v>
+        <v>24.392</v>
       </c>
       <c r="G9">
         <v>60.6</v>
@@ -2025,28 +2025,28 @@
         <v>113.8</v>
       </c>
       <c r="M9">
-        <v>1.0735529</v>
+        <v>1.2269176</v>
       </c>
       <c r="N9">
-        <v>112.7264471</v>
+        <v>112.5730824</v>
       </c>
       <c r="O9">
-        <v>28.181611775</v>
+        <v>28.1432706</v>
       </c>
       <c r="P9">
-        <v>84.54483532500001</v>
+        <v>84.42981180000001</v>
       </c>
       <c r="Q9">
-        <v>91.84483532500001</v>
+        <v>91.72981180000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1257296556791092</v>
+        <v>0.12639286224797</v>
       </c>
       <c r="T9">
-        <v>1.16307388145442</v>
+        <v>1.172724345123972</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>106.0031601609944</v>
+        <v>92.75276514087008</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1192994332681324</v>
+        <v>0.1190295367546933</v>
       </c>
       <c r="C10">
-        <v>281.8844540945554</v>
+        <v>279.0764449724667</v>
       </c>
       <c r="D10">
-        <v>245.6764540945554</v>
+        <v>245.9174449724667</v>
       </c>
       <c r="E10">
-        <v>8.592000000000002</v>
+        <v>11.641</v>
       </c>
       <c r="F10">
-        <v>24.392</v>
+        <v>27.441</v>
       </c>
       <c r="G10">
         <v>60.6</v>
@@ -2107,28 +2107,28 @@
         <v>113.8</v>
       </c>
       <c r="M10">
-        <v>1.2269176</v>
+        <v>1.3802823</v>
       </c>
       <c r="N10">
-        <v>112.5730824</v>
+        <v>112.4197177</v>
       </c>
       <c r="O10">
-        <v>28.1432706</v>
+        <v>28.104929425</v>
       </c>
       <c r="P10">
-        <v>84.42981180000001</v>
+        <v>84.314788275</v>
       </c>
       <c r="Q10">
-        <v>91.72981180000001</v>
+        <v>91.614788275</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.12639286224797</v>
+        <v>0.1270706447853773</v>
       </c>
       <c r="T10">
-        <v>1.172724345123972</v>
+        <v>1.182586906896152</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>92.75276514087008</v>
+        <v>82.44690234744009</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1190295367546933</v>
+        <v>0.1187596402412542</v>
       </c>
       <c r="C11">
-        <v>279.0764449724667</v>
+        <v>276.2689091039371</v>
       </c>
       <c r="D11">
-        <v>245.9174449724667</v>
+        <v>246.1589091039371</v>
       </c>
       <c r="E11">
-        <v>11.641</v>
+        <v>14.69</v>
       </c>
       <c r="F11">
-        <v>27.441</v>
+        <v>30.49</v>
       </c>
       <c r="G11">
         <v>60.6</v>
@@ -2189,28 +2189,28 @@
         <v>113.8</v>
       </c>
       <c r="M11">
-        <v>1.3802823</v>
+        <v>1.533647</v>
       </c>
       <c r="N11">
-        <v>112.4197177</v>
+        <v>112.266353</v>
       </c>
       <c r="O11">
-        <v>28.104929425</v>
+        <v>28.06658825</v>
       </c>
       <c r="P11">
-        <v>84.314788275</v>
+        <v>84.19976475</v>
       </c>
       <c r="Q11">
-        <v>91.614788275</v>
+        <v>91.49976475</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1270706447853773</v>
+        <v>0.1277634891569491</v>
       </c>
       <c r="T11">
-        <v>1.182586906896152</v>
+        <v>1.192668636707713</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>82.44690234744009</v>
+        <v>74.20221211269607</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1187596402412542</v>
+        <v>0.1184897437278151</v>
       </c>
       <c r="C12">
-        <v>276.2689091039371</v>
+        <v>273.4618478843868</v>
       </c>
       <c r="D12">
-        <v>246.1589091039371</v>
+        <v>246.4008478843868</v>
       </c>
       <c r="E12">
-        <v>14.69</v>
+        <v>17.739</v>
       </c>
       <c r="F12">
-        <v>30.49000000000001</v>
+        <v>33.539</v>
       </c>
       <c r="G12">
         <v>60.6</v>
@@ -2271,28 +2271,28 @@
         <v>113.8</v>
       </c>
       <c r="M12">
-        <v>1.533647</v>
+        <v>1.6870117</v>
       </c>
       <c r="N12">
-        <v>112.266353</v>
+        <v>112.1129883</v>
       </c>
       <c r="O12">
-        <v>28.06658825</v>
+        <v>28.028247075</v>
       </c>
       <c r="P12">
-        <v>84.19976475</v>
+        <v>84.084741225</v>
       </c>
       <c r="Q12">
-        <v>91.49976475</v>
+        <v>91.384741225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1277634891569491</v>
+        <v>0.1284719030649608</v>
       </c>
       <c r="T12">
-        <v>1.192668636707713</v>
+        <v>1.202976922245377</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>74.20221211269606</v>
+        <v>67.45655646608733</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1184897437278151</v>
+        <v>0.118219847214376</v>
       </c>
       <c r="C13">
-        <v>273.4618478843868</v>
+        <v>270.6552627147277</v>
       </c>
       <c r="D13">
-        <v>246.4008478843868</v>
+        <v>246.6432627147277</v>
       </c>
       <c r="E13">
-        <v>17.739</v>
+        <v>20.788</v>
       </c>
       <c r="F13">
-        <v>33.539</v>
+        <v>36.588</v>
       </c>
       <c r="G13">
         <v>60.6</v>
@@ -2353,28 +2353,28 @@
         <v>113.8</v>
       </c>
       <c r="M13">
-        <v>1.6870117</v>
+        <v>1.8403764</v>
       </c>
       <c r="N13">
-        <v>112.1129883</v>
+        <v>111.9596236</v>
       </c>
       <c r="O13">
-        <v>28.028247075</v>
+        <v>27.9899059</v>
       </c>
       <c r="P13">
-        <v>84.084741225</v>
+        <v>83.9697177</v>
       </c>
       <c r="Q13">
-        <v>91.384741225</v>
+        <v>91.2697177</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1284719030649608</v>
+        <v>0.1291964172890636</v>
       </c>
       <c r="T13">
-        <v>1.202976922245377</v>
+        <v>1.213519486999806</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>67.45655646608733</v>
+        <v>61.83517676058006</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.118219847214376</v>
+        <v>0.1179499507009369</v>
       </c>
       <c r="C14">
-        <v>270.6552627147277</v>
+        <v>267.8491550013902</v>
       </c>
       <c r="D14">
-        <v>246.6432627147277</v>
+        <v>246.8861550013902</v>
       </c>
       <c r="E14">
-        <v>20.788</v>
+        <v>23.83700000000001</v>
       </c>
       <c r="F14">
-        <v>36.588</v>
+        <v>39.63700000000001</v>
       </c>
       <c r="G14">
         <v>60.6</v>
@@ -2435,28 +2435,28 @@
         <v>113.8</v>
       </c>
       <c r="M14">
-        <v>1.8403764</v>
+        <v>1.9937411</v>
       </c>
       <c r="N14">
-        <v>111.9596236</v>
+        <v>111.8062589</v>
       </c>
       <c r="O14">
-        <v>27.9899059</v>
+        <v>27.951564725</v>
       </c>
       <c r="P14">
-        <v>83.9697177</v>
+        <v>83.85469417500001</v>
       </c>
       <c r="Q14">
-        <v>91.2697177</v>
+        <v>91.154694175</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1291964172890636</v>
+        <v>0.1299375870125711</v>
       </c>
       <c r="T14">
-        <v>1.213519486999806</v>
+        <v>1.224304409564682</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>61.83517676058006</v>
+        <v>57.0786247020739</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1179499507009369</v>
+        <v>0.1176800541874977</v>
       </c>
       <c r="C15">
-        <v>267.8491550013902</v>
+        <v>265.0435261563499</v>
       </c>
       <c r="D15">
-        <v>246.8861550013902</v>
+        <v>247.1295261563499</v>
       </c>
       <c r="E15">
-        <v>23.83700000000001</v>
+        <v>26.88600000000001</v>
       </c>
       <c r="F15">
-        <v>39.63700000000001</v>
+        <v>42.68600000000001</v>
       </c>
       <c r="G15">
         <v>60.6</v>
@@ -2517,28 +2517,28 @@
         <v>113.8</v>
       </c>
       <c r="M15">
-        <v>1.9937411</v>
+        <v>2.1471058</v>
       </c>
       <c r="N15">
-        <v>111.8062589</v>
+        <v>111.6528942</v>
       </c>
       <c r="O15">
-        <v>27.951564725</v>
+        <v>27.91322355</v>
       </c>
       <c r="P15">
-        <v>83.85469417500001</v>
+        <v>83.73967064999999</v>
       </c>
       <c r="Q15">
-        <v>91.154694175</v>
+        <v>91.03967064999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1299375870125711</v>
+        <v>0.1306959932412765</v>
       </c>
       <c r="T15">
-        <v>1.224304409564682</v>
+        <v>1.235340144282229</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>57.0786247020739</v>
+        <v>53.00158008049718</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1176800541874977</v>
+        <v>0.1174101576740586</v>
       </c>
       <c r="C16">
-        <v>265.0435261563499</v>
+        <v>262.2383775971556</v>
       </c>
       <c r="D16">
-        <v>247.1295261563499</v>
+        <v>247.3733775971557</v>
       </c>
       <c r="E16">
-        <v>26.88600000000001</v>
+        <v>29.93500000000001</v>
       </c>
       <c r="F16">
-        <v>42.68600000000001</v>
+        <v>45.73500000000001</v>
       </c>
       <c r="G16">
         <v>60.6</v>
@@ -2599,28 +2599,28 @@
         <v>113.8</v>
       </c>
       <c r="M16">
-        <v>2.1471058</v>
+        <v>2.300470500000001</v>
       </c>
       <c r="N16">
-        <v>111.6528942</v>
+        <v>111.4995295</v>
       </c>
       <c r="O16">
-        <v>27.91322355</v>
+        <v>27.874882375</v>
       </c>
       <c r="P16">
-        <v>83.73967064999999</v>
+        <v>83.624647125</v>
       </c>
       <c r="Q16">
-        <v>91.03967064999999</v>
+        <v>90.92464712499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1306959932412765</v>
+        <v>0.1314722443224219</v>
       </c>
       <c r="T16">
-        <v>1.235340144282229</v>
+        <v>1.246635543346071</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>53.00158008049718</v>
+        <v>49.46814140846404</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1174101576740586</v>
+        <v>0.1171402611606195</v>
       </c>
       <c r="C17">
-        <v>262.2383775971556</v>
+        <v>259.433710746957</v>
       </c>
       <c r="D17">
-        <v>247.3733775971557</v>
+        <v>247.617710746957</v>
       </c>
       <c r="E17">
-        <v>29.93500000000001</v>
+        <v>32.98400000000001</v>
       </c>
       <c r="F17">
-        <v>45.73500000000001</v>
+        <v>48.78400000000001</v>
       </c>
       <c r="G17">
         <v>60.6</v>
@@ -2681,28 +2681,28 @@
         <v>113.8</v>
       </c>
       <c r="M17">
-        <v>2.3004705</v>
+        <v>2.4538352</v>
       </c>
       <c r="N17">
-        <v>111.4995295</v>
+        <v>111.3461648</v>
       </c>
       <c r="O17">
-        <v>27.874882375</v>
+        <v>27.8365412</v>
       </c>
       <c r="P17">
-        <v>83.624647125</v>
+        <v>83.5096236</v>
       </c>
       <c r="Q17">
-        <v>90.92464712499999</v>
+        <v>90.80962359999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1314722443224219</v>
+        <v>0.1322669775721661</v>
       </c>
       <c r="T17">
-        <v>1.246635543346071</v>
+        <v>1.258199880482862</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>49.46814140846404</v>
+        <v>46.37638257043504</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1171402611606195</v>
+        <v>0.1168703646471804</v>
       </c>
       <c r="C18">
-        <v>259.433710746957</v>
+        <v>256.6295270345313</v>
       </c>
       <c r="D18">
-        <v>247.617710746957</v>
+        <v>247.8625270345314</v>
       </c>
       <c r="E18">
-        <v>32.98400000000001</v>
+        <v>36.03300000000002</v>
       </c>
       <c r="F18">
-        <v>48.78400000000001</v>
+        <v>51.83300000000001</v>
       </c>
       <c r="G18">
         <v>60.6</v>
@@ -2763,28 +2763,28 @@
         <v>113.8</v>
       </c>
       <c r="M18">
-        <v>2.4538352</v>
+        <v>2.6071999</v>
       </c>
       <c r="N18">
-        <v>111.3461648</v>
+        <v>111.1928001</v>
       </c>
       <c r="O18">
-        <v>27.8365412</v>
+        <v>27.798200025</v>
       </c>
       <c r="P18">
-        <v>83.5096236</v>
+        <v>83.394600075</v>
       </c>
       <c r="Q18">
-        <v>90.80962359999999</v>
+        <v>90.694600075</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1322669775721661</v>
+        <v>0.1330808610206993</v>
       </c>
       <c r="T18">
-        <v>1.258199880482862</v>
+        <v>1.270042876345841</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>46.37638257043504</v>
+        <v>43.6483600662918</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1168703646471804</v>
+        <v>0.1166004681337413</v>
       </c>
       <c r="C19">
-        <v>256.6295270345313</v>
+        <v>253.8258278943123</v>
       </c>
       <c r="D19">
-        <v>247.8625270345314</v>
+        <v>248.1078278943123</v>
       </c>
       <c r="E19">
-        <v>36.03300000000002</v>
+        <v>39.08200000000001</v>
       </c>
       <c r="F19">
-        <v>51.83300000000001</v>
+        <v>54.88200000000001</v>
       </c>
       <c r="G19">
         <v>60.6</v>
@@ -2845,28 +2845,28 @@
         <v>113.8</v>
       </c>
       <c r="M19">
-        <v>2.6071999</v>
+        <v>2.7605646</v>
       </c>
       <c r="N19">
-        <v>111.1928001</v>
+        <v>111.0394354</v>
       </c>
       <c r="O19">
-        <v>27.798200025</v>
+        <v>27.75985885</v>
       </c>
       <c r="P19">
-        <v>83.394600075</v>
+        <v>83.27957655</v>
       </c>
       <c r="Q19">
-        <v>90.694600075</v>
+        <v>90.57957655</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1330808610206993</v>
+        <v>0.1339145952850503</v>
       </c>
       <c r="T19">
-        <v>1.270042876345841</v>
+        <v>1.282174725766453</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>43.6483600662918</v>
+        <v>41.22345117372004</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1166004681337413</v>
+        <v>0.1163305716203022</v>
       </c>
       <c r="C20">
-        <v>253.8258278943123</v>
+        <v>251.0226147664174</v>
       </c>
       <c r="D20">
-        <v>248.1078278943123</v>
+        <v>248.3536147664175</v>
       </c>
       <c r="E20">
-        <v>39.08200000000001</v>
+        <v>42.131</v>
       </c>
       <c r="F20">
-        <v>54.88200000000001</v>
+        <v>57.931</v>
       </c>
       <c r="G20">
         <v>60.6</v>
@@ -2927,28 +2927,28 @@
         <v>113.8</v>
       </c>
       <c r="M20">
-        <v>2.7605646</v>
+        <v>2.9139293</v>
       </c>
       <c r="N20">
-        <v>111.0394354</v>
+        <v>110.8860707</v>
       </c>
       <c r="O20">
-        <v>27.75985885</v>
+        <v>27.721517675</v>
       </c>
       <c r="P20">
-        <v>83.27957655</v>
+        <v>83.16455302499999</v>
       </c>
       <c r="Q20">
-        <v>90.57957655</v>
+        <v>90.46455302499999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1339145952850503</v>
+        <v>0.13476891558062</v>
       </c>
       <c r="T20">
-        <v>1.282174725766453</v>
+        <v>1.294606127024612</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>41.22345117372004</v>
+        <v>39.05379584878741</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1163305716203022</v>
+        <v>0.1160606751068631</v>
       </c>
       <c r="C21">
-        <v>251.0226147664174</v>
+        <v>248.2198890966768</v>
       </c>
       <c r="D21">
-        <v>248.3536147664175</v>
+        <v>248.5998890966768</v>
       </c>
       <c r="E21">
-        <v>42.131</v>
+        <v>45.18000000000001</v>
       </c>
       <c r="F21">
-        <v>57.931</v>
+        <v>60.98000000000001</v>
       </c>
       <c r="G21">
         <v>60.6</v>
@@ -3009,28 +3009,28 @@
         <v>113.8</v>
       </c>
       <c r="M21">
-        <v>2.9139293</v>
+        <v>3.067294</v>
       </c>
       <c r="N21">
-        <v>110.8860707</v>
+        <v>110.732706</v>
       </c>
       <c r="O21">
-        <v>27.721517675</v>
+        <v>27.6831765</v>
       </c>
       <c r="P21">
-        <v>83.16455302499999</v>
+        <v>83.04952949999999</v>
       </c>
       <c r="Q21">
-        <v>90.46455302499999</v>
+        <v>90.34952949999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.13476891558062</v>
+        <v>0.1356445938835788</v>
       </c>
       <c r="T21">
-        <v>1.294606127024612</v>
+        <v>1.307348313314224</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>39.05379584878741</v>
+        <v>37.10110605634803</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1160606751068631</v>
+        <v>0.115790778593424</v>
       </c>
       <c r="C22">
-        <v>248.2198890966768</v>
+        <v>245.4176523366608</v>
       </c>
       <c r="D22">
-        <v>248.5998890966768</v>
+        <v>248.8466523366608</v>
       </c>
       <c r="E22">
-        <v>45.18000000000001</v>
+        <v>48.22900000000001</v>
       </c>
       <c r="F22">
-        <v>60.98000000000001</v>
+        <v>64.02900000000001</v>
       </c>
       <c r="G22">
         <v>60.6</v>
@@ -3091,28 +3091,28 @@
         <v>113.8</v>
       </c>
       <c r="M22">
-        <v>3.067294</v>
+        <v>3.2206587</v>
       </c>
       <c r="N22">
-        <v>110.732706</v>
+        <v>110.5793413</v>
       </c>
       <c r="O22">
-        <v>27.6831765</v>
+        <v>27.644835325</v>
       </c>
       <c r="P22">
-        <v>83.04952949999999</v>
+        <v>82.93450597499999</v>
       </c>
       <c r="Q22">
-        <v>90.34952949999999</v>
+        <v>90.23450597499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1356445938835788</v>
+        <v>0.1365424412574987</v>
       </c>
       <c r="T22">
-        <v>1.307348313314224</v>
+        <v>1.32041308659851</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>37.10110605634803</v>
+        <v>35.33438672033146</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.115790778593424</v>
+        <v>0.1155208820799848</v>
       </c>
       <c r="C23">
-        <v>245.4176523366608</v>
+        <v>242.615905943709</v>
       </c>
       <c r="D23">
-        <v>248.8466523366608</v>
+        <v>249.093905943709</v>
       </c>
       <c r="E23">
-        <v>48.22900000000001</v>
+        <v>51.27800000000001</v>
       </c>
       <c r="F23">
-        <v>64.02900000000001</v>
+        <v>67.078</v>
       </c>
       <c r="G23">
         <v>60.6</v>
@@ -3173,28 +3173,28 @@
         <v>113.8</v>
       </c>
       <c r="M23">
-        <v>3.2206587</v>
+        <v>3.3740234</v>
       </c>
       <c r="N23">
-        <v>110.5793413</v>
+        <v>110.4259766</v>
       </c>
       <c r="O23">
-        <v>27.644835325</v>
+        <v>27.60649415</v>
       </c>
       <c r="P23">
-        <v>82.93450597499999</v>
+        <v>82.81948245</v>
       </c>
       <c r="Q23">
-        <v>90.23450597499999</v>
+        <v>90.11948244999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1365424412574987</v>
+        <v>0.1374633103589549</v>
       </c>
       <c r="T23">
-        <v>1.32041308659851</v>
+        <v>1.333812854069573</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>35.33438672033146</v>
+        <v>33.72827823304367</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1155208820799848</v>
+        <v>0.1152509855665457</v>
       </c>
       <c r="C24">
-        <v>242.615905943709</v>
+        <v>239.8146513809588</v>
       </c>
       <c r="D24">
-        <v>249.093905943709</v>
+        <v>249.3416513809588</v>
       </c>
       <c r="E24">
-        <v>51.27800000000001</v>
+        <v>54.32700000000001</v>
       </c>
       <c r="F24">
-        <v>67.078</v>
+        <v>70.12700000000001</v>
       </c>
       <c r="G24">
         <v>60.6</v>
@@ -3255,28 +3255,28 @@
         <v>113.8</v>
       </c>
       <c r="M24">
-        <v>3.3740234</v>
+        <v>3.5273881</v>
       </c>
       <c r="N24">
-        <v>110.4259766</v>
+        <v>110.2726119</v>
       </c>
       <c r="O24">
-        <v>27.60649415</v>
+        <v>27.568152975</v>
       </c>
       <c r="P24">
-        <v>82.81948245</v>
+        <v>82.704458925</v>
       </c>
       <c r="Q24">
-        <v>90.11948244999999</v>
+        <v>90.00445892499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1374633103589549</v>
+        <v>0.1384080981383711</v>
       </c>
       <c r="T24">
-        <v>1.333812854069573</v>
+        <v>1.347560667448974</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>33.72827823304367</v>
+        <v>32.26183135334612</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1152509855665457</v>
+        <v>0.1149810890531066</v>
       </c>
       <c r="C25">
-        <v>239.8146513809588</v>
+        <v>237.0138901173742</v>
       </c>
       <c r="D25">
-        <v>249.3416513809588</v>
+        <v>249.5898901173742</v>
       </c>
       <c r="E25">
-        <v>54.32700000000001</v>
+        <v>57.37600000000002</v>
       </c>
       <c r="F25">
-        <v>70.12700000000001</v>
+        <v>73.17600000000002</v>
       </c>
       <c r="G25">
         <v>60.6</v>
@@ -3337,28 +3337,28 @@
         <v>113.8</v>
       </c>
       <c r="M25">
-        <v>3.5273881</v>
+        <v>3.6807528</v>
       </c>
       <c r="N25">
-        <v>110.2726119</v>
+        <v>110.1192472</v>
       </c>
       <c r="O25">
-        <v>27.568152975</v>
+        <v>27.5298118</v>
       </c>
       <c r="P25">
-        <v>82.704458925</v>
+        <v>82.58943539999999</v>
       </c>
       <c r="Q25">
-        <v>90.00445892499999</v>
+        <v>89.88943539999998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1384080981383711</v>
+        <v>0.1393777487540876</v>
       </c>
       <c r="T25">
-        <v>1.347560667448974</v>
+        <v>1.361670265390992</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>32.26183135334612</v>
+        <v>30.91758838029002</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1149810890531066</v>
+        <v>0.1147111925396675</v>
       </c>
       <c r="C26">
-        <v>237.0138901173742</v>
+        <v>234.2136236277751</v>
       </c>
       <c r="D26">
-        <v>249.5898901173742</v>
+        <v>249.8386236277751</v>
       </c>
       <c r="E26">
-        <v>57.376</v>
+        <v>60.42500000000001</v>
       </c>
       <c r="F26">
-        <v>73.176</v>
+        <v>76.22500000000001</v>
       </c>
       <c r="G26">
         <v>60.6</v>
@@ -3419,28 +3419,28 @@
         <v>113.8</v>
       </c>
       <c r="M26">
-        <v>3.6807528</v>
+        <v>3.8341175</v>
       </c>
       <c r="N26">
-        <v>110.1192472</v>
+        <v>109.9658825</v>
       </c>
       <c r="O26">
-        <v>27.5298118</v>
+        <v>27.491470625</v>
       </c>
       <c r="P26">
-        <v>82.5894354</v>
+        <v>82.47441187499999</v>
       </c>
       <c r="Q26">
-        <v>89.8894354</v>
+        <v>89.77441187499998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1393777487540876</v>
+        <v>0.1403732567195567</v>
       </c>
       <c r="T26">
-        <v>1.361670265390992</v>
+        <v>1.37615611927813</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>30.91758838029003</v>
+        <v>29.68088484507843</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1147111925396675</v>
+        <v>0.1144412960262284</v>
       </c>
       <c r="C27">
-        <v>234.2136236277751</v>
+        <v>231.413853392866</v>
       </c>
       <c r="D27">
-        <v>249.8386236277751</v>
+        <v>250.087853392866</v>
       </c>
       <c r="E27">
-        <v>60.42500000000001</v>
+        <v>63.47400000000002</v>
       </c>
       <c r="F27">
-        <v>76.22500000000001</v>
+        <v>79.27400000000002</v>
       </c>
       <c r="G27">
         <v>60.6</v>
@@ -3501,28 +3501,28 @@
         <v>113.8</v>
       </c>
       <c r="M27">
-        <v>3.8341175</v>
+        <v>3.987482200000001</v>
       </c>
       <c r="N27">
-        <v>109.9658825</v>
+        <v>109.8125178</v>
       </c>
       <c r="O27">
-        <v>27.491470625</v>
+        <v>27.45312945</v>
       </c>
       <c r="P27">
-        <v>82.47441187499999</v>
+        <v>82.35938834999999</v>
       </c>
       <c r="Q27">
-        <v>89.77441187499998</v>
+        <v>89.65938834999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1403732567195567</v>
+        <v>0.141395670305714</v>
       </c>
       <c r="T27">
-        <v>1.37615611927813</v>
+        <v>1.391033482729786</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>29.68088484507843</v>
+        <v>28.53931235103695</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1144412960262284</v>
+        <v>0.1141713995127893</v>
       </c>
       <c r="C28">
-        <v>231.413853392866</v>
+        <v>228.6145808992659</v>
       </c>
       <c r="D28">
-        <v>250.087853392866</v>
+        <v>250.3375808992659</v>
       </c>
       <c r="E28">
-        <v>63.47400000000002</v>
+        <v>66.52300000000002</v>
       </c>
       <c r="F28">
-        <v>79.27400000000002</v>
+        <v>82.32300000000002</v>
       </c>
       <c r="G28">
         <v>60.6</v>
@@ -3583,28 +3583,28 @@
         <v>113.8</v>
       </c>
       <c r="M28">
-        <v>3.987482200000001</v>
+        <v>4.140846900000001</v>
       </c>
       <c r="N28">
-        <v>109.8125178</v>
+        <v>109.6591531</v>
       </c>
       <c r="O28">
-        <v>27.45312945</v>
+        <v>27.414788275</v>
       </c>
       <c r="P28">
-        <v>82.35938834999999</v>
+        <v>82.24436482499999</v>
       </c>
       <c r="Q28">
-        <v>89.65938834999999</v>
+        <v>89.54436482499999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.141395670305714</v>
+        <v>0.142446095222999</v>
       </c>
       <c r="T28">
-        <v>1.391033482729786</v>
+        <v>1.406318445180117</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>28.53931235103695</v>
+        <v>27.48230078248002</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1141713995127893</v>
+        <v>0.1139015029993502</v>
       </c>
       <c r="C29">
-        <v>228.6145808992659</v>
+        <v>225.8158076395376</v>
       </c>
       <c r="D29">
-        <v>250.3375808992659</v>
+        <v>250.5878076395376</v>
       </c>
       <c r="E29">
-        <v>66.52300000000002</v>
+        <v>69.57200000000002</v>
       </c>
       <c r="F29">
-        <v>82.32300000000002</v>
+        <v>85.37200000000001</v>
       </c>
       <c r="G29">
         <v>60.6</v>
@@ -3665,28 +3665,28 @@
         <v>113.8</v>
       </c>
       <c r="M29">
-        <v>4.140846900000001</v>
+        <v>4.294211600000001</v>
       </c>
       <c r="N29">
-        <v>109.6591531</v>
+        <v>109.5057884</v>
       </c>
       <c r="O29">
-        <v>27.414788275</v>
+        <v>27.3764471</v>
       </c>
       <c r="P29">
-        <v>82.24436482499999</v>
+        <v>82.12934129999999</v>
       </c>
       <c r="Q29">
-        <v>89.54436482499999</v>
+        <v>89.42934129999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.142446095222999</v>
+        <v>0.1435256986102086</v>
       </c>
       <c r="T29">
-        <v>1.406318445180117</v>
+        <v>1.422027989920735</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>27.48230078248002</v>
+        <v>26.5007900402486</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1139015029993502</v>
+        <v>0.113631606485911</v>
       </c>
       <c r="C30">
-        <v>225.8158076395376</v>
+        <v>223.0175351122175</v>
       </c>
       <c r="D30">
-        <v>250.5878076395376</v>
+        <v>250.8385351122175</v>
       </c>
       <c r="E30">
-        <v>69.57200000000002</v>
+        <v>72.62100000000002</v>
       </c>
       <c r="F30">
-        <v>85.37200000000001</v>
+        <v>88.42100000000002</v>
       </c>
       <c r="G30">
         <v>60.6</v>
@@ -3747,28 +3747,28 @@
         <v>113.8</v>
       </c>
       <c r="M30">
-        <v>4.294211600000001</v>
+        <v>4.447576300000001</v>
       </c>
       <c r="N30">
-        <v>109.5057884</v>
+        <v>109.3524237</v>
       </c>
       <c r="O30">
-        <v>27.3764471</v>
+        <v>27.338105925</v>
       </c>
       <c r="P30">
-        <v>82.12934129999999</v>
+        <v>82.01431777499999</v>
       </c>
       <c r="Q30">
-        <v>89.42934129999999</v>
+        <v>89.31431777499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1435256986102086</v>
+        <v>0.1446357133604381</v>
       </c>
       <c r="T30">
-        <v>1.422027989920735</v>
+        <v>1.438180057048412</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>26.5007900402486</v>
+        <v>25.58696969403313</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.113631606485911</v>
+        <v>0.1133617099724719</v>
       </c>
       <c r="C31">
-        <v>223.0175351122175</v>
+        <v>220.2197648218453</v>
       </c>
       <c r="D31">
-        <v>250.8385351122175</v>
+        <v>251.0897648218454</v>
       </c>
       <c r="E31">
-        <v>72.62100000000001</v>
+        <v>75.67000000000002</v>
       </c>
       <c r="F31">
-        <v>88.42100000000001</v>
+        <v>91.47000000000001</v>
       </c>
       <c r="G31">
         <v>60.6</v>
@@ -3829,28 +3829,28 @@
         <v>113.8</v>
       </c>
       <c r="M31">
-        <v>4.4475763</v>
+        <v>4.600941000000001</v>
       </c>
       <c r="N31">
-        <v>109.3524237</v>
+        <v>109.199059</v>
       </c>
       <c r="O31">
-        <v>27.338105925</v>
+        <v>27.29976475</v>
       </c>
       <c r="P31">
-        <v>82.01431777499999</v>
+        <v>81.89929425</v>
       </c>
       <c r="Q31">
-        <v>89.31431777499999</v>
+        <v>89.19929424999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1446357133604381</v>
+        <v>0.145777442817817</v>
       </c>
       <c r="T31">
-        <v>1.438180057048412</v>
+        <v>1.454793611808309</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>25.58696969403313</v>
+        <v>24.73407070423202</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1133617099724719</v>
+        <v>0.1130918134590328</v>
       </c>
       <c r="C32">
-        <v>220.2197648218453</v>
+        <v>217.4224982789946</v>
       </c>
       <c r="D32">
-        <v>251.0897648218454</v>
+        <v>251.3414982789946</v>
       </c>
       <c r="E32">
-        <v>75.67000000000002</v>
+        <v>78.71900000000001</v>
       </c>
       <c r="F32">
-        <v>91.47000000000001</v>
+        <v>94.51900000000001</v>
       </c>
       <c r="G32">
         <v>60.6</v>
@@ -3911,28 +3911,28 @@
         <v>113.8</v>
       </c>
       <c r="M32">
-        <v>4.600941000000001</v>
+        <v>4.7543057</v>
       </c>
       <c r="N32">
-        <v>109.199059</v>
+        <v>109.0456943</v>
       </c>
       <c r="O32">
-        <v>27.29976475</v>
+        <v>27.261423575</v>
       </c>
       <c r="P32">
-        <v>81.89929425</v>
+        <v>81.784270725</v>
       </c>
       <c r="Q32">
-        <v>89.19929424999999</v>
+        <v>89.084270725</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.145777442817817</v>
+        <v>0.1469522658826563</v>
       </c>
       <c r="T32">
-        <v>1.454793611808309</v>
+        <v>1.471888718880087</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>24.73407070423202</v>
+        <v>23.93619745570841</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1130918134590328</v>
+        <v>0.1128219169455937</v>
       </c>
       <c r="C33">
-        <v>217.4224982789946</v>
+        <v>214.6257370003027</v>
       </c>
       <c r="D33">
-        <v>251.3414982789946</v>
+        <v>251.5937370003027</v>
       </c>
       <c r="E33">
-        <v>78.71900000000001</v>
+        <v>81.76800000000001</v>
       </c>
       <c r="F33">
-        <v>94.51900000000001</v>
+        <v>97.56800000000001</v>
       </c>
       <c r="G33">
         <v>60.6</v>
@@ -3993,28 +3993,28 @@
         <v>113.8</v>
       </c>
       <c r="M33">
-        <v>4.7543057</v>
+        <v>4.907670400000001</v>
       </c>
       <c r="N33">
-        <v>109.0456943</v>
+        <v>108.8923296</v>
       </c>
       <c r="O33">
-        <v>27.261423575</v>
+        <v>27.2230824</v>
       </c>
       <c r="P33">
-        <v>81.784270725</v>
+        <v>81.6692472</v>
       </c>
       <c r="Q33">
-        <v>89.084270725</v>
+        <v>88.9692472</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1469522658826563</v>
+        <v>0.1481616425670496</v>
       </c>
       <c r="T33">
-        <v>1.471888718880087</v>
+        <v>1.489486623218683</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>23.93619745570841</v>
+        <v>23.18819128521752</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1128219169455937</v>
+        <v>0.1125520204321546</v>
       </c>
       <c r="C34">
-        <v>214.6257370003027</v>
+        <v>211.829482508501</v>
       </c>
       <c r="D34">
-        <v>251.5937370003027</v>
+        <v>251.846482508501</v>
       </c>
       <c r="E34">
-        <v>81.76800000000001</v>
+        <v>84.81700000000002</v>
       </c>
       <c r="F34">
-        <v>97.56800000000001</v>
+        <v>100.617</v>
       </c>
       <c r="G34">
         <v>60.6</v>
@@ -4075,28 +4075,28 @@
         <v>113.8</v>
       </c>
       <c r="M34">
-        <v>4.907670400000001</v>
+        <v>5.061035100000001</v>
       </c>
       <c r="N34">
-        <v>108.8923296</v>
+        <v>108.7389649</v>
       </c>
       <c r="O34">
-        <v>27.2230824</v>
+        <v>27.184741225</v>
       </c>
       <c r="P34">
-        <v>81.6692472</v>
+        <v>81.554223675</v>
       </c>
       <c r="Q34">
-        <v>88.9692472</v>
+        <v>88.854223675</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1481616425670496</v>
+        <v>0.1494071200479919</v>
       </c>
       <c r="T34">
-        <v>1.489486623218683</v>
+        <v>1.507609838134549</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>23.18819128521752</v>
+        <v>22.48551882202911</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1125520204321546</v>
+        <v>0.1122821239187155</v>
       </c>
       <c r="C35">
-        <v>211.829482508501</v>
+        <v>209.0337363324464</v>
       </c>
       <c r="D35">
-        <v>251.846482508501</v>
+        <v>252.0997363324464</v>
       </c>
       <c r="E35">
-        <v>84.81700000000002</v>
+        <v>87.86600000000003</v>
       </c>
       <c r="F35">
-        <v>100.617</v>
+        <v>103.666</v>
       </c>
       <c r="G35">
         <v>60.6</v>
@@ -4157,28 +4157,28 @@
         <v>113.8</v>
       </c>
       <c r="M35">
-        <v>5.061035100000001</v>
+        <v>5.214399800000001</v>
       </c>
       <c r="N35">
-        <v>108.7389649</v>
+        <v>108.5856002</v>
       </c>
       <c r="O35">
-        <v>27.184741225</v>
+        <v>27.14640005</v>
       </c>
       <c r="P35">
-        <v>81.554223675</v>
+        <v>81.43920015</v>
       </c>
       <c r="Q35">
-        <v>88.854223675</v>
+        <v>88.73920015</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1494071200479919</v>
+        <v>0.150690339270781</v>
       </c>
       <c r="T35">
-        <v>1.507609838134549</v>
+        <v>1.526282241381199</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>22.48551882202911</v>
+        <v>21.8241800331459</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1122821239187155</v>
+        <v>0.1120122274052764</v>
       </c>
       <c r="C36">
-        <v>209.0337363324464</v>
+        <v>206.238500007151</v>
       </c>
       <c r="D36">
-        <v>252.0997363324464</v>
+        <v>252.353500007151</v>
       </c>
       <c r="E36">
-        <v>87.86600000000003</v>
+        <v>90.91500000000002</v>
       </c>
       <c r="F36">
-        <v>103.666</v>
+        <v>106.715</v>
       </c>
       <c r="G36">
         <v>60.6</v>
@@ -4239,28 +4239,28 @@
         <v>113.8</v>
       </c>
       <c r="M36">
-        <v>5.214399800000001</v>
+        <v>5.367764500000001</v>
       </c>
       <c r="N36">
-        <v>108.5856002</v>
+        <v>108.4322355</v>
       </c>
       <c r="O36">
-        <v>27.14640005</v>
+        <v>27.108058875</v>
       </c>
       <c r="P36">
-        <v>81.43920015</v>
+        <v>81.32417662499999</v>
       </c>
       <c r="Q36">
-        <v>88.73920015</v>
+        <v>88.62417662499999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.150690339270781</v>
+        <v>0.1520130421619637</v>
       </c>
       <c r="T36">
-        <v>1.526282241381199</v>
+        <v>1.545529180112362</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>21.8241800331459</v>
+        <v>21.20063203219888</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1120122274052764</v>
+        <v>0.1117423308918372</v>
       </c>
       <c r="C37">
-        <v>206.238500007151</v>
+        <v>203.4437750738142</v>
       </c>
       <c r="D37">
-        <v>252.353500007151</v>
+        <v>252.6077750738142</v>
       </c>
       <c r="E37">
-        <v>90.91500000000002</v>
+        <v>93.96400000000003</v>
       </c>
       <c r="F37">
-        <v>106.715</v>
+        <v>109.764</v>
       </c>
       <c r="G37">
         <v>60.6</v>
@@ -4321,28 +4321,28 @@
         <v>113.8</v>
       </c>
       <c r="M37">
-        <v>5.367764500000001</v>
+        <v>5.521129200000001</v>
       </c>
       <c r="N37">
-        <v>108.4322355</v>
+        <v>108.2788708</v>
       </c>
       <c r="O37">
-        <v>27.108058875</v>
+        <v>27.0697177</v>
       </c>
       <c r="P37">
-        <v>81.32417662499999</v>
+        <v>81.20915309999999</v>
       </c>
       <c r="Q37">
-        <v>88.62417662499999</v>
+        <v>88.50915309999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1520130421619637</v>
+        <v>0.1533770795184957</v>
       </c>
       <c r="T37">
-        <v>1.545529180112362</v>
+        <v>1.565377585678873</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>21.20063203219888</v>
+        <v>20.61172558686002</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1117423308918373</v>
+        <v>0.1114724343783981</v>
       </c>
       <c r="C38">
-        <v>203.4437750738142</v>
+        <v>200.649563079853</v>
       </c>
       <c r="D38">
-        <v>252.6077750738142</v>
+        <v>252.8625630798531</v>
       </c>
       <c r="E38">
-        <v>93.96400000000001</v>
+        <v>97.01300000000002</v>
       </c>
       <c r="F38">
-        <v>109.764</v>
+        <v>112.813</v>
       </c>
       <c r="G38">
         <v>60.6</v>
@@ -4403,28 +4403,28 @@
         <v>113.8</v>
       </c>
       <c r="M38">
-        <v>5.5211292</v>
+        <v>5.674493900000001</v>
       </c>
       <c r="N38">
-        <v>108.2788708</v>
+        <v>108.1255061</v>
       </c>
       <c r="O38">
-        <v>27.0697177</v>
+        <v>27.031376525</v>
       </c>
       <c r="P38">
-        <v>81.20915309999999</v>
+        <v>81.094129575</v>
       </c>
       <c r="Q38">
-        <v>88.50915309999999</v>
+        <v>88.39412957499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1533770795184957</v>
+        <v>0.154784419648251</v>
       </c>
       <c r="T38">
-        <v>1.565377585678873</v>
+        <v>1.585856099358607</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>20.61172558686002</v>
+        <v>20.05465192235029</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1114724343783981</v>
+        <v>0.111202537864959</v>
       </c>
       <c r="C39">
-        <v>200.649563079853</v>
+        <v>197.8558655789342</v>
       </c>
       <c r="D39">
-        <v>252.8625630798531</v>
+        <v>253.1178655789342</v>
       </c>
       <c r="E39">
-        <v>97.01300000000002</v>
+        <v>100.062</v>
       </c>
       <c r="F39">
-        <v>112.813</v>
+        <v>115.862</v>
       </c>
       <c r="G39">
         <v>60.6</v>
@@ -4485,28 +4485,28 @@
         <v>113.8</v>
       </c>
       <c r="M39">
-        <v>5.674493900000001</v>
+        <v>5.8278586</v>
       </c>
       <c r="N39">
-        <v>108.1255061</v>
+        <v>107.9721414</v>
       </c>
       <c r="O39">
-        <v>27.031376525</v>
+        <v>26.99303535</v>
       </c>
       <c r="P39">
-        <v>81.094129575</v>
+        <v>80.97910605</v>
       </c>
       <c r="Q39">
-        <v>88.39412957499999</v>
+        <v>88.27910605</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.154784419648251</v>
+        <v>0.1562371578467081</v>
       </c>
       <c r="T39">
-        <v>1.585856099358607</v>
+        <v>1.606995210253817</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>20.05465192235029</v>
+        <v>19.5268979243937</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.111202537864959</v>
+        <v>0.1109326413515199</v>
       </c>
       <c r="C40">
-        <v>197.8558655789342</v>
+        <v>195.0626841310051</v>
       </c>
       <c r="D40">
-        <v>253.1178655789342</v>
+        <v>253.3736841310051</v>
       </c>
       <c r="E40">
-        <v>100.062</v>
+        <v>103.111</v>
       </c>
       <c r="F40">
-        <v>115.862</v>
+        <v>118.911</v>
       </c>
       <c r="G40">
         <v>60.6</v>
@@ -4567,28 +4567,28 @@
         <v>113.8</v>
       </c>
       <c r="M40">
-        <v>5.8278586</v>
+        <v>5.981223300000001</v>
       </c>
       <c r="N40">
-        <v>107.9721414</v>
+        <v>107.8187767</v>
       </c>
       <c r="O40">
-        <v>26.99303535</v>
+        <v>26.954694175</v>
       </c>
       <c r="P40">
-        <v>80.97910605</v>
+        <v>80.864082525</v>
       </c>
       <c r="Q40">
-        <v>88.27910605</v>
+        <v>88.164082525</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1562371578467081</v>
+        <v>0.1577375268057704</v>
       </c>
       <c r="T40">
-        <v>1.606995210253817</v>
+        <v>1.628827406752148</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>19.5268979243937</v>
+        <v>19.02620823402463</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1109326413515199</v>
+        <v>0.1106627448380808</v>
       </c>
       <c r="C41">
-        <v>195.0626841310051</v>
+        <v>192.2700203023261</v>
       </c>
       <c r="D41">
-        <v>253.3736841310051</v>
+        <v>253.6300203023262</v>
       </c>
       <c r="E41">
-        <v>103.111</v>
+        <v>106.16</v>
       </c>
       <c r="F41">
-        <v>118.911</v>
+        <v>121.96</v>
       </c>
       <c r="G41">
         <v>60.6</v>
@@ -4649,28 +4649,28 @@
         <v>113.8</v>
       </c>
       <c r="M41">
-        <v>5.981223300000001</v>
+        <v>6.134588000000001</v>
       </c>
       <c r="N41">
-        <v>107.8187767</v>
+        <v>107.665412</v>
       </c>
       <c r="O41">
-        <v>26.954694175</v>
+        <v>26.916353</v>
       </c>
       <c r="P41">
-        <v>80.864082525</v>
+        <v>80.749059</v>
       </c>
       <c r="Q41">
-        <v>88.164082525</v>
+        <v>88.049059</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1577375268057704</v>
+        <v>0.159287908063468</v>
       </c>
       <c r="T41">
-        <v>1.628827406752148</v>
+        <v>1.651387343133757</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>19.02620823402463</v>
+        <v>18.55055302817402</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1106627448380808</v>
+        <v>0.1103928483246417</v>
       </c>
       <c r="C42">
-        <v>192.2700203023261</v>
+        <v>189.4778756655024</v>
       </c>
       <c r="D42">
-        <v>253.6300203023262</v>
+        <v>253.8868756655024</v>
       </c>
       <c r="E42">
-        <v>106.16</v>
+        <v>109.209</v>
       </c>
       <c r="F42">
-        <v>121.96</v>
+        <v>125.009</v>
       </c>
       <c r="G42">
         <v>60.6</v>
@@ -4731,28 +4731,28 @@
         <v>113.8</v>
       </c>
       <c r="M42">
-        <v>6.134588000000001</v>
+        <v>6.287952700000001</v>
       </c>
       <c r="N42">
-        <v>107.665412</v>
+        <v>107.5120473</v>
       </c>
       <c r="O42">
-        <v>26.916353</v>
+        <v>26.878011825</v>
       </c>
       <c r="P42">
-        <v>80.749059</v>
+        <v>80.63403547499999</v>
       </c>
       <c r="Q42">
-        <v>88.049059</v>
+        <v>87.93403547499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.159287908063468</v>
+        <v>0.1608908446180368</v>
       </c>
       <c r="T42">
-        <v>1.651387343133757</v>
+        <v>1.674712023121522</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>18.55055302817402</v>
+        <v>18.09810051529172</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1103928483246417</v>
+        <v>0.1101229518112026</v>
       </c>
       <c r="C43">
-        <v>189.4778756655024</v>
+        <v>186.6862517995156</v>
       </c>
       <c r="D43">
-        <v>253.8868756655024</v>
+        <v>254.1442517995156</v>
       </c>
       <c r="E43">
-        <v>109.209</v>
+        <v>112.258</v>
       </c>
       <c r="F43">
-        <v>125.009</v>
+        <v>128.058</v>
       </c>
       <c r="G43">
         <v>60.6</v>
@@ -4813,28 +4813,28 @@
         <v>113.8</v>
       </c>
       <c r="M43">
-        <v>6.287952700000001</v>
+        <v>6.441317400000001</v>
       </c>
       <c r="N43">
-        <v>107.5120473</v>
+        <v>107.3586826</v>
       </c>
       <c r="O43">
-        <v>26.878011825</v>
+        <v>26.83967065</v>
       </c>
       <c r="P43">
-        <v>80.63403547499999</v>
+        <v>80.51901194999999</v>
       </c>
       <c r="Q43">
-        <v>87.93403547499999</v>
+        <v>87.81901194999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1608908446180368</v>
+        <v>0.162549054846901</v>
       </c>
       <c r="T43">
-        <v>1.674712023121522</v>
+        <v>1.698841002419209</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>18.09810051529172</v>
+        <v>17.66719336016573</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1101229518112026</v>
+        <v>0.1098530552977635</v>
       </c>
       <c r="C44">
-        <v>186.6862517995156</v>
+        <v>183.895150289757</v>
       </c>
       <c r="D44">
-        <v>254.1442517995156</v>
+        <v>254.402150289757</v>
       </c>
       <c r="E44">
-        <v>112.258</v>
+        <v>115.307</v>
       </c>
       <c r="F44">
-        <v>128.058</v>
+        <v>131.107</v>
       </c>
       <c r="G44">
         <v>60.6</v>
@@ -4895,28 +4895,28 @@
         <v>113.8</v>
       </c>
       <c r="M44">
-        <v>6.441317400000001</v>
+        <v>6.5946821</v>
       </c>
       <c r="N44">
-        <v>107.3586826</v>
+        <v>107.2053179</v>
       </c>
       <c r="O44">
-        <v>26.83967065</v>
+        <v>26.801329475</v>
       </c>
       <c r="P44">
-        <v>80.51901194999999</v>
+        <v>80.40398842499999</v>
       </c>
       <c r="Q44">
-        <v>87.81901194999999</v>
+        <v>87.70398842499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.162549054846901</v>
+        <v>0.1642654478908131</v>
       </c>
       <c r="T44">
-        <v>1.698841002419209</v>
+        <v>1.723816612569447</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>17.66719336016573</v>
+        <v>17.25632839830141</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1098530552977635</v>
+        <v>0.1095831587843244</v>
       </c>
       <c r="C45">
-        <v>183.895150289757</v>
+        <v>181.1045727280593</v>
       </c>
       <c r="D45">
-        <v>254.402150289757</v>
+        <v>254.6605727280593</v>
       </c>
       <c r="E45">
-        <v>115.307</v>
+        <v>118.356</v>
       </c>
       <c r="F45">
-        <v>131.107</v>
+        <v>134.156</v>
       </c>
       <c r="G45">
         <v>60.6</v>
@@ -4977,28 +4977,28 @@
         <v>113.8</v>
       </c>
       <c r="M45">
-        <v>6.5946821</v>
+        <v>6.7480468</v>
       </c>
       <c r="N45">
-        <v>107.2053179</v>
+        <v>107.0519532</v>
       </c>
       <c r="O45">
-        <v>26.801329475</v>
+        <v>26.7629883</v>
       </c>
       <c r="P45">
-        <v>80.40398842499999</v>
+        <v>80.2889649</v>
       </c>
       <c r="Q45">
-        <v>87.70398842499999</v>
+        <v>87.58896489999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1642654478908131</v>
+        <v>0.1660431406862935</v>
       </c>
       <c r="T45">
-        <v>1.723816612569447</v>
+        <v>1.74968420879648</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>17.25632839830141</v>
+        <v>16.86413911652183</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1095831587843244</v>
+        <v>0.1093132622708852</v>
       </c>
       <c r="C46">
-        <v>181.1045727280593</v>
+        <v>178.3145207127302</v>
       </c>
       <c r="D46">
-        <v>254.6605727280593</v>
+        <v>254.9195207127302</v>
       </c>
       <c r="E46">
-        <v>118.356</v>
+        <v>121.405</v>
       </c>
       <c r="F46">
-        <v>134.156</v>
+        <v>137.205</v>
       </c>
       <c r="G46">
         <v>60.6</v>
@@ -5059,28 +5059,28 @@
         <v>113.8</v>
       </c>
       <c r="M46">
-        <v>6.7480468</v>
+        <v>6.9014115</v>
       </c>
       <c r="N46">
-        <v>107.0519532</v>
+        <v>106.8985885</v>
       </c>
       <c r="O46">
-        <v>26.7629883</v>
+        <v>26.724647125</v>
       </c>
       <c r="P46">
-        <v>80.2889649</v>
+        <v>80.173941375</v>
       </c>
       <c r="Q46">
-        <v>87.58896489999999</v>
+        <v>87.473941375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1660431406862935</v>
+        <v>0.167885476856155</v>
       </c>
       <c r="T46">
-        <v>1.74968420879648</v>
+        <v>1.776492444886314</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>16.86413911652183</v>
+        <v>16.48938046948802</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1093132622708852</v>
+        <v>0.1090433657574461</v>
       </c>
       <c r="C47">
-        <v>178.3145207127302</v>
+        <v>175.5249958485844</v>
       </c>
       <c r="D47">
-        <v>254.9195207127302</v>
+        <v>255.1789958485844</v>
       </c>
       <c r="E47">
-        <v>121.405</v>
+        <v>124.454</v>
       </c>
       <c r="F47">
-        <v>137.205</v>
+        <v>140.254</v>
       </c>
       <c r="G47">
         <v>60.6</v>
@@ -5141,28 +5141,28 @@
         <v>113.8</v>
       </c>
       <c r="M47">
-        <v>6.9014115</v>
+        <v>7.054776200000001</v>
       </c>
       <c r="N47">
-        <v>106.8985885</v>
+        <v>106.7452238</v>
       </c>
       <c r="O47">
-        <v>26.724647125</v>
+        <v>26.68630595</v>
       </c>
       <c r="P47">
-        <v>80.173941375</v>
+        <v>80.05891785</v>
       </c>
       <c r="Q47">
-        <v>87.473941375</v>
+        <v>87.35891785</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.167885476856155</v>
+        <v>0.1697960476989743</v>
       </c>
       <c r="T47">
-        <v>1.776492444886314</v>
+        <v>1.804293578609104</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>16.48938046948802</v>
+        <v>16.13091567667306</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1090433657574461</v>
+        <v>0.108773469244007</v>
       </c>
       <c r="C48">
-        <v>175.5249958485844</v>
+        <v>172.7359997469775</v>
       </c>
       <c r="D48">
-        <v>255.1789958485844</v>
+        <v>255.4389997469775</v>
       </c>
       <c r="E48">
-        <v>124.454</v>
+        <v>127.503</v>
       </c>
       <c r="F48">
-        <v>140.254</v>
+        <v>143.303</v>
       </c>
       <c r="G48">
         <v>60.6</v>
@@ -5223,28 +5223,28 @@
         <v>113.8</v>
       </c>
       <c r="M48">
-        <v>7.054776200000001</v>
+        <v>7.208140900000001</v>
       </c>
       <c r="N48">
-        <v>106.7452238</v>
+        <v>106.5918591</v>
       </c>
       <c r="O48">
-        <v>26.68630595</v>
+        <v>26.647964775</v>
       </c>
       <c r="P48">
-        <v>80.05891785</v>
+        <v>79.943894325</v>
       </c>
       <c r="Q48">
-        <v>87.35891785</v>
+        <v>87.243894325</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1697960476989743</v>
+        <v>0.1717787155547302</v>
       </c>
       <c r="T48">
-        <v>1.804293578609104</v>
+        <v>1.83314381171766</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>16.13091567667306</v>
+        <v>15.78770470482895</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.108773469244007</v>
+        <v>0.1085035727305679</v>
       </c>
       <c r="C49">
-        <v>172.7359997469775</v>
+        <v>169.947534025839</v>
       </c>
       <c r="D49">
-        <v>255.4389997469775</v>
+        <v>255.6995340258391</v>
       </c>
       <c r="E49">
-        <v>127.503</v>
+        <v>130.552</v>
       </c>
       <c r="F49">
-        <v>143.303</v>
+        <v>146.352</v>
       </c>
       <c r="G49">
         <v>60.6</v>
@@ -5305,28 +5305,28 @@
         <v>113.8</v>
       </c>
       <c r="M49">
-        <v>7.208140900000001</v>
+        <v>7.361505600000001</v>
       </c>
       <c r="N49">
-        <v>106.5918591</v>
+        <v>106.4384944</v>
       </c>
       <c r="O49">
-        <v>26.647964775</v>
+        <v>26.6096236</v>
       </c>
       <c r="P49">
-        <v>79.943894325</v>
+        <v>79.8288708</v>
       </c>
       <c r="Q49">
-        <v>87.243894325</v>
+        <v>87.1288708</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1717787155547302</v>
+        <v>0.1738376398664767</v>
       </c>
       <c r="T49">
-        <v>1.83314381171766</v>
+        <v>1.863103669176546</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>15.78770470482895</v>
+        <v>15.45879419014501</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1085035727305679</v>
+        <v>0.1082336762171288</v>
       </c>
       <c r="C50">
-        <v>169.9475340258391</v>
+        <v>167.159600309706</v>
       </c>
       <c r="D50">
-        <v>255.6995340258391</v>
+        <v>255.960600309706</v>
       </c>
       <c r="E50">
-        <v>130.552</v>
+        <v>133.601</v>
       </c>
       <c r="F50">
-        <v>146.352</v>
+        <v>149.401</v>
       </c>
       <c r="G50">
         <v>60.6</v>
@@ -5387,28 +5387,28 @@
         <v>113.8</v>
       </c>
       <c r="M50">
-        <v>7.3615056</v>
+        <v>7.5148703</v>
       </c>
       <c r="N50">
-        <v>106.4384944</v>
+        <v>106.2851297</v>
       </c>
       <c r="O50">
-        <v>26.6096236</v>
+        <v>26.571282425</v>
       </c>
       <c r="P50">
-        <v>79.8288708</v>
+        <v>79.71384727500001</v>
       </c>
       <c r="Q50">
-        <v>87.1288708</v>
+        <v>87.013847275</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1738376398664767</v>
+        <v>0.1759773063080957</v>
       </c>
       <c r="T50">
-        <v>1.863103669176546</v>
+        <v>1.894238423006368</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>15.45879419014502</v>
+        <v>15.14330859442777</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1082336762171288</v>
+        <v>0.1079637797036897</v>
       </c>
       <c r="C51">
-        <v>167.159600309706</v>
+        <v>164.3722002297569</v>
       </c>
       <c r="D51">
-        <v>255.960600309706</v>
+        <v>256.2222002297569</v>
       </c>
       <c r="E51">
-        <v>133.601</v>
+        <v>136.65</v>
       </c>
       <c r="F51">
-        <v>149.401</v>
+        <v>152.45</v>
       </c>
       <c r="G51">
         <v>60.6</v>
@@ -5469,28 +5469,28 @@
         <v>113.8</v>
       </c>
       <c r="M51">
-        <v>7.5148703</v>
+        <v>7.668235</v>
       </c>
       <c r="N51">
-        <v>106.2851297</v>
+        <v>106.131765</v>
       </c>
       <c r="O51">
-        <v>26.571282425</v>
+        <v>26.53294125</v>
       </c>
       <c r="P51">
-        <v>79.71384727500001</v>
+        <v>79.59882375000001</v>
       </c>
       <c r="Q51">
-        <v>87.013847275</v>
+        <v>86.89882375000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1759773063080957</v>
+        <v>0.1782025594073793</v>
       </c>
       <c r="T51">
-        <v>1.894238423006368</v>
+        <v>1.926618566989383</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>15.14330859442777</v>
+        <v>14.84044242253922</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1079637797036897</v>
+        <v>0.1076938831902506</v>
       </c>
       <c r="C52">
-        <v>164.3722002297569</v>
+        <v>161.5853354238454</v>
       </c>
       <c r="D52">
-        <v>256.2222002297569</v>
+        <v>256.4843354238454</v>
       </c>
       <c r="E52">
-        <v>136.65</v>
+        <v>139.699</v>
       </c>
       <c r="F52">
-        <v>152.45</v>
+        <v>155.499</v>
       </c>
       <c r="G52">
         <v>60.6</v>
@@ -5551,28 +5551,28 @@
         <v>113.8</v>
       </c>
       <c r="M52">
-        <v>7.668235</v>
+        <v>7.821599700000001</v>
       </c>
       <c r="N52">
-        <v>106.131765</v>
+        <v>105.9784003</v>
       </c>
       <c r="O52">
-        <v>26.53294125</v>
+        <v>26.494600075</v>
       </c>
       <c r="P52">
-        <v>79.59882375000001</v>
+        <v>79.483800225</v>
       </c>
       <c r="Q52">
-        <v>86.89882375000001</v>
+        <v>86.78380022499999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1782025594073793</v>
+        <v>0.1805186391637767</v>
       </c>
       <c r="T52">
-        <v>1.926618566989383</v>
+        <v>1.960320349502317</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>14.84044242253922</v>
+        <v>14.5494533554306</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1076938831902506</v>
+        <v>0.1074239866768114</v>
       </c>
       <c r="C53">
-        <v>161.5853354238454</v>
+        <v>158.7990075365346</v>
       </c>
       <c r="D53">
-        <v>256.4843354238454</v>
+        <v>256.7470075365346</v>
       </c>
       <c r="E53">
-        <v>139.699</v>
+        <v>142.748</v>
       </c>
       <c r="F53">
-        <v>155.499</v>
+        <v>158.548</v>
       </c>
       <c r="G53">
         <v>60.6</v>
@@ -5633,28 +5633,28 @@
         <v>113.8</v>
       </c>
       <c r="M53">
-        <v>7.821599700000001</v>
+        <v>7.974964400000001</v>
       </c>
       <c r="N53">
-        <v>105.9784003</v>
+        <v>105.8250356</v>
       </c>
       <c r="O53">
-        <v>26.494600075</v>
+        <v>26.4562589</v>
       </c>
       <c r="P53">
-        <v>79.483800225</v>
+        <v>79.3687767</v>
       </c>
       <c r="Q53">
-        <v>86.78380022499999</v>
+        <v>86.6687767</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1805186391637767</v>
+        <v>0.1829312222433572</v>
       </c>
       <c r="T53">
-        <v>1.960320349502317</v>
+        <v>1.995426372953289</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>14.5494533554306</v>
+        <v>14.26965617551847</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1074239866768114</v>
+        <v>0.1071540901633723</v>
       </c>
       <c r="C54">
-        <v>158.7990075365346</v>
+        <v>156.0132182191315</v>
       </c>
       <c r="D54">
-        <v>256.7470075365346</v>
+        <v>257.0102182191315</v>
       </c>
       <c r="E54">
-        <v>142.748</v>
+        <v>145.797</v>
       </c>
       <c r="F54">
-        <v>158.548</v>
+        <v>161.597</v>
       </c>
       <c r="G54">
         <v>60.6</v>
@@ -5715,28 +5715,28 @@
         <v>113.8</v>
       </c>
       <c r="M54">
-        <v>7.974964400000001</v>
+        <v>8.128329100000002</v>
       </c>
       <c r="N54">
-        <v>105.8250356</v>
+        <v>105.6716709</v>
       </c>
       <c r="O54">
-        <v>26.4562589</v>
+        <v>26.417917725</v>
       </c>
       <c r="P54">
-        <v>79.3687767</v>
+        <v>79.253753175</v>
       </c>
       <c r="Q54">
-        <v>86.6687767</v>
+        <v>86.553753175</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1829312222433572</v>
+        <v>0.1854464684327071</v>
       </c>
       <c r="T54">
-        <v>1.995426372953289</v>
+        <v>2.032026269742601</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>14.26965617551847</v>
+        <v>14.00041737975397</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1071540901633723</v>
+        <v>0.1068841936499332</v>
       </c>
       <c r="C55">
-        <v>156.0132182191315</v>
+        <v>153.2279691297216</v>
       </c>
       <c r="D55">
-        <v>257.0102182191315</v>
+        <v>257.2739691297216</v>
       </c>
       <c r="E55">
-        <v>145.797</v>
+        <v>148.846</v>
       </c>
       <c r="F55">
-        <v>161.597</v>
+        <v>164.646</v>
       </c>
       <c r="G55">
         <v>60.6</v>
@@ -5797,28 +5797,28 @@
         <v>113.8</v>
       </c>
       <c r="M55">
-        <v>8.128329100000002</v>
+        <v>8.281693800000001</v>
       </c>
       <c r="N55">
-        <v>105.6716709</v>
+        <v>105.5183062</v>
       </c>
       <c r="O55">
-        <v>26.417917725</v>
+        <v>26.37957655</v>
       </c>
       <c r="P55">
-        <v>79.253753175</v>
+        <v>79.13872965</v>
       </c>
       <c r="Q55">
-        <v>86.553753175</v>
+        <v>86.43872965</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1854464684327071</v>
+        <v>0.1880710731520287</v>
       </c>
       <c r="T55">
-        <v>2.032026269742601</v>
+        <v>2.070217466392318</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>14.00041737975397</v>
+        <v>13.74115039124001</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1068841936499332</v>
+        <v>0.1066142971364941</v>
       </c>
       <c r="C56">
-        <v>153.2279691297216</v>
+        <v>150.4432619332037</v>
       </c>
       <c r="D56">
-        <v>257.2739691297216</v>
+        <v>257.5382619332037</v>
       </c>
       <c r="E56">
-        <v>148.846</v>
+        <v>151.895</v>
       </c>
       <c r="F56">
-        <v>164.646</v>
+        <v>167.695</v>
       </c>
       <c r="G56">
         <v>60.6</v>
@@ -5879,28 +5879,28 @@
         <v>113.8</v>
       </c>
       <c r="M56">
-        <v>8.281693800000001</v>
+        <v>8.4350585</v>
       </c>
       <c r="N56">
-        <v>105.5183062</v>
+        <v>105.3649415</v>
       </c>
       <c r="O56">
-        <v>26.37957655</v>
+        <v>26.341235375</v>
       </c>
       <c r="P56">
-        <v>79.13872965</v>
+        <v>79.023706125</v>
       </c>
       <c r="Q56">
-        <v>86.43872965</v>
+        <v>86.323706125</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1880710731520287</v>
+        <v>0.1908123269699869</v>
       </c>
       <c r="T56">
-        <v>2.070217466392318</v>
+        <v>2.1101060495598</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>13.74115039124001</v>
+        <v>13.49131129321747</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1066142971364941</v>
+        <v>0.106344400623055</v>
       </c>
       <c r="C57">
-        <v>150.4432619332037</v>
+        <v>147.6590983013249</v>
       </c>
       <c r="D57">
-        <v>257.5382619332037</v>
+        <v>257.8030983013249</v>
       </c>
       <c r="E57">
-        <v>151.895</v>
+        <v>154.944</v>
       </c>
       <c r="F57">
-        <v>167.695</v>
+        <v>170.744</v>
       </c>
       <c r="G57">
         <v>60.6</v>
@@ -5961,28 +5961,28 @@
         <v>113.8</v>
       </c>
       <c r="M57">
-        <v>8.4350585</v>
+        <v>8.588423200000001</v>
       </c>
       <c r="N57">
-        <v>105.3649415</v>
+        <v>105.2115768</v>
       </c>
       <c r="O57">
-        <v>26.341235375</v>
+        <v>26.3028942</v>
       </c>
       <c r="P57">
-        <v>79.023706125</v>
+        <v>78.90868259999999</v>
       </c>
       <c r="Q57">
-        <v>86.323706125</v>
+        <v>86.20868259999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1908123269699869</v>
+        <v>0.1936781832342159</v>
       </c>
       <c r="T57">
-        <v>2.1101060495598</v>
+        <v>2.151807750143986</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>13.49131129321747</v>
+        <v>13.2503950201243</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.106344400623055</v>
+        <v>0.1060745041096159</v>
       </c>
       <c r="C58">
-        <v>147.6590983013249</v>
+        <v>144.8754799127157</v>
       </c>
       <c r="D58">
-        <v>257.8030983013249</v>
+        <v>258.0684799127158</v>
       </c>
       <c r="E58">
-        <v>154.944</v>
+        <v>157.993</v>
       </c>
       <c r="F58">
-        <v>170.744</v>
+        <v>173.793</v>
       </c>
       <c r="G58">
         <v>60.6</v>
@@ -6043,28 +6043,28 @@
         <v>113.8</v>
       </c>
       <c r="M58">
-        <v>8.588423200000001</v>
+        <v>8.741787900000002</v>
       </c>
       <c r="N58">
-        <v>105.2115768</v>
+        <v>105.0582121</v>
       </c>
       <c r="O58">
-        <v>26.3028942</v>
+        <v>26.264553025</v>
       </c>
       <c r="P58">
-        <v>78.90868259999999</v>
+        <v>78.79365907499999</v>
       </c>
       <c r="Q58">
-        <v>86.20868259999999</v>
+        <v>86.09365907499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1936781832342159</v>
+        <v>0.1966773351386416</v>
       </c>
       <c r="T58">
-        <v>2.151807750143986</v>
+        <v>2.195449064708832</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>13.2503950201243</v>
+        <v>13.0179319495958</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1060745041096159</v>
+        <v>0.1064571075961768</v>
       </c>
       <c r="C59">
-        <v>144.8754799127157</v>
+        <v>141.4504382034789</v>
       </c>
       <c r="D59">
-        <v>258.0684799127158</v>
+        <v>257.692438203479</v>
       </c>
       <c r="E59">
-        <v>157.993</v>
+        <v>161.042</v>
       </c>
       <c r="F59">
-        <v>173.793</v>
+        <v>176.842</v>
       </c>
       <c r="G59">
         <v>60.6</v>
@@ -6125,45 +6125,45 @@
         <v>113.8</v>
       </c>
       <c r="M59">
-        <v>8.741787900000002</v>
+        <v>9.160415600000002</v>
       </c>
       <c r="N59">
-        <v>105.0582121</v>
+        <v>104.6395844</v>
       </c>
       <c r="O59">
-        <v>26.264553025</v>
+        <v>26.1598961</v>
       </c>
       <c r="P59">
-        <v>78.79365907499999</v>
+        <v>78.47968829999999</v>
       </c>
       <c r="Q59">
-        <v>86.09365907499999</v>
+        <v>85.77968829999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1966773351386416</v>
+        <v>0.1998193038004209</v>
       </c>
       <c r="T59">
-        <v>2.195449064708832</v>
+        <v>2.241168537110099</v>
       </c>
       <c r="U59">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y59">
-        <v>13.0179319495958</v>
+        <v>12.42301713909137</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1064571075961768</v>
+        <v>0.1061984610827376</v>
       </c>
       <c r="C60">
-        <v>141.450438203479</v>
+        <v>138.6555287148391</v>
       </c>
       <c r="D60">
-        <v>257.692438203479</v>
+        <v>257.9465287148391</v>
       </c>
       <c r="E60">
-        <v>161.042</v>
+        <v>164.091</v>
       </c>
       <c r="F60">
-        <v>176.842</v>
+        <v>179.891</v>
       </c>
       <c r="G60">
         <v>60.6</v>
@@ -6207,28 +6207,28 @@
         <v>113.8</v>
       </c>
       <c r="M60">
-        <v>9.1604156</v>
+        <v>9.318353800000001</v>
       </c>
       <c r="N60">
-        <v>104.6395844</v>
+        <v>104.4816462</v>
       </c>
       <c r="O60">
-        <v>26.1598961</v>
+        <v>26.12041155</v>
       </c>
       <c r="P60">
-        <v>78.47968829999999</v>
+        <v>78.36123465</v>
       </c>
       <c r="Q60">
-        <v>85.77968829999999</v>
+        <v>85.66123465</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1998193038004209</v>
+        <v>0.2031145392261894</v>
       </c>
       <c r="T60">
-        <v>2.241168537110098</v>
+        <v>2.28911822767728</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>12.42301713909137</v>
+        <v>12.2124575265644</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1061984610827376</v>
+        <v>0.1059398145692985</v>
       </c>
       <c r="C61">
-        <v>138.6555287148391</v>
+        <v>135.8611207986225</v>
       </c>
       <c r="D61">
-        <v>257.9465287148391</v>
+        <v>258.2011207986225</v>
       </c>
       <c r="E61">
-        <v>164.091</v>
+        <v>167.14</v>
       </c>
       <c r="F61">
-        <v>179.891</v>
+        <v>182.94</v>
       </c>
       <c r="G61">
         <v>60.6</v>
@@ -6289,28 +6289,28 @@
         <v>113.8</v>
       </c>
       <c r="M61">
-        <v>9.318353800000001</v>
+        <v>9.476292000000001</v>
       </c>
       <c r="N61">
-        <v>104.4816462</v>
+        <v>104.323708</v>
       </c>
       <c r="O61">
-        <v>26.12041155</v>
+        <v>26.080927</v>
       </c>
       <c r="P61">
-        <v>78.36123465</v>
+        <v>78.24278099999999</v>
       </c>
       <c r="Q61">
-        <v>85.66123465</v>
+        <v>85.54278099999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2031145392261894</v>
+        <v>0.2065745364232464</v>
       </c>
       <c r="T61">
-        <v>2.28911822767728</v>
+        <v>2.339465402772822</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>12.2124575265644</v>
+        <v>12.00891656778833</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1059398145692985</v>
+        <v>0.1056811680558594</v>
       </c>
       <c r="C62">
-        <v>135.8611207986225</v>
+        <v>133.0672159414459</v>
       </c>
       <c r="D62">
-        <v>258.2011207986225</v>
+        <v>258.4562159414459</v>
       </c>
       <c r="E62">
-        <v>167.14</v>
+        <v>170.189</v>
       </c>
       <c r="F62">
-        <v>182.94</v>
+        <v>185.989</v>
       </c>
       <c r="G62">
         <v>60.6</v>
@@ -6371,28 +6371,28 @@
         <v>113.8</v>
       </c>
       <c r="M62">
-        <v>9.476292000000001</v>
+        <v>9.634230199999999</v>
       </c>
       <c r="N62">
-        <v>104.323708</v>
+        <v>104.1657698</v>
       </c>
       <c r="O62">
-        <v>26.080927</v>
+        <v>26.04144245</v>
       </c>
       <c r="P62">
-        <v>78.24278099999999</v>
+        <v>78.12432734999999</v>
       </c>
       <c r="Q62">
-        <v>85.54278099999999</v>
+        <v>85.42432734999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2065745364232464</v>
+        <v>0.2102119693739986</v>
       </c>
       <c r="T62">
-        <v>2.339465402772822</v>
+        <v>2.392394484283519</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>12.00891656778833</v>
+        <v>11.81204908307049</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1056811680558594</v>
+        <v>0.1054225215424203</v>
       </c>
       <c r="C63">
-        <v>133.0672159414459</v>
+        <v>130.2738156358066</v>
       </c>
       <c r="D63">
-        <v>258.4562159414459</v>
+        <v>258.7118156358066</v>
       </c>
       <c r="E63">
-        <v>170.189</v>
+        <v>173.238</v>
       </c>
       <c r="F63">
-        <v>185.989</v>
+        <v>189.038</v>
       </c>
       <c r="G63">
         <v>60.6</v>
@@ -6453,28 +6453,28 @@
         <v>113.8</v>
       </c>
       <c r="M63">
-        <v>9.634230199999999</v>
+        <v>9.7921684</v>
       </c>
       <c r="N63">
-        <v>104.1657698</v>
+        <v>104.0078316</v>
       </c>
       <c r="O63">
-        <v>26.04144245</v>
+        <v>26.0019579</v>
       </c>
       <c r="P63">
-        <v>78.12432734999999</v>
+        <v>78.0058737</v>
       </c>
       <c r="Q63">
-        <v>85.42432734999998</v>
+        <v>85.30587369999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2102119693739986</v>
+        <v>0.214040846164264</v>
       </c>
       <c r="T63">
-        <v>2.392394484283519</v>
+        <v>2.448109306926359</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>11.81204908307049</v>
+        <v>11.6215321623758</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1054225215424203</v>
+        <v>0.1051638750289812</v>
       </c>
       <c r="C64">
-        <v>130.2738156358066</v>
+        <v>127.4809213801118</v>
       </c>
       <c r="D64">
-        <v>258.7118156358066</v>
+        <v>258.9679213801118</v>
       </c>
       <c r="E64">
-        <v>173.238</v>
+        <v>176.287</v>
       </c>
       <c r="F64">
-        <v>189.038</v>
+        <v>192.087</v>
       </c>
       <c r="G64">
         <v>60.6</v>
@@ -6535,28 +6535,28 @@
         <v>113.8</v>
       </c>
       <c r="M64">
-        <v>9.7921684</v>
+        <v>9.9501066</v>
       </c>
       <c r="N64">
-        <v>104.0078316</v>
+        <v>103.8498934</v>
       </c>
       <c r="O64">
-        <v>26.0019579</v>
+        <v>25.96247335</v>
       </c>
       <c r="P64">
-        <v>78.0058737</v>
+        <v>77.88742005</v>
       </c>
       <c r="Q64">
-        <v>85.30587369999999</v>
+        <v>85.18742005</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.214040846164264</v>
+        <v>0.2180766892675168</v>
       </c>
       <c r="T64">
-        <v>2.448109306926359</v>
+        <v>2.506835741603946</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>11.6215321623758</v>
+        <v>11.43706339789365</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1051638750289812</v>
+        <v>0.1049052285155421</v>
       </c>
       <c r="C65">
-        <v>127.4809213801118</v>
+        <v>124.6885346787078</v>
       </c>
       <c r="D65">
-        <v>258.9679213801118</v>
+        <v>259.2245346787078</v>
       </c>
       <c r="E65">
-        <v>176.287</v>
+        <v>179.336</v>
       </c>
       <c r="F65">
-        <v>192.087</v>
+        <v>195.136</v>
       </c>
       <c r="G65">
         <v>60.6</v>
@@ -6617,28 +6617,28 @@
         <v>113.8</v>
       </c>
       <c r="M65">
-        <v>9.9501066</v>
+        <v>10.1080448</v>
       </c>
       <c r="N65">
-        <v>103.8498934</v>
+        <v>103.6919552</v>
       </c>
       <c r="O65">
-        <v>25.96247335</v>
+        <v>25.9229888</v>
       </c>
       <c r="P65">
-        <v>77.88742005</v>
+        <v>77.7689664</v>
       </c>
       <c r="Q65">
-        <v>85.18742005</v>
+        <v>85.06896639999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2180766892675168</v>
+        <v>0.2223367458765058</v>
       </c>
       <c r="T65">
-        <v>2.506835741603946</v>
+        <v>2.568824755985844</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>11.43706339789365</v>
+        <v>11.25835928230156</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1049052285155421</v>
+        <v>0.104646582002103</v>
       </c>
       <c r="C66">
-        <v>124.6885346787078</v>
+        <v>121.8966570419094</v>
       </c>
       <c r="D66">
-        <v>259.2245346787078</v>
+        <v>259.4816570419094</v>
       </c>
       <c r="E66">
-        <v>179.336</v>
+        <v>182.385</v>
       </c>
       <c r="F66">
-        <v>195.136</v>
+        <v>198.185</v>
       </c>
       <c r="G66">
         <v>60.6</v>
@@ -6699,28 +6699,28 @@
         <v>113.8</v>
       </c>
       <c r="M66">
-        <v>10.1080448</v>
+        <v>10.265983</v>
       </c>
       <c r="N66">
-        <v>103.6919552</v>
+        <v>103.534017</v>
       </c>
       <c r="O66">
-        <v>25.9229888</v>
+        <v>25.88350425</v>
       </c>
       <c r="P66">
-        <v>77.7689664</v>
+        <v>77.65051274999999</v>
       </c>
       <c r="Q66">
-        <v>85.06896639999999</v>
+        <v>84.95051274999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2223367458765058</v>
+        <v>0.2268402342917228</v>
       </c>
       <c r="T66">
-        <v>2.568824755985844</v>
+        <v>2.634355999760993</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>11.25835928230156</v>
+        <v>11.08515375488153</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.104646582002103</v>
+        <v>0.1043879354886638</v>
       </c>
       <c r="C67">
-        <v>121.8966570419094</v>
+        <v>119.10528998603</v>
       </c>
       <c r="D67">
-        <v>259.4816570419094</v>
+        <v>259.73928998603</v>
       </c>
       <c r="E67">
-        <v>182.385</v>
+        <v>185.434</v>
       </c>
       <c r="F67">
-        <v>198.185</v>
+        <v>201.234</v>
       </c>
       <c r="G67">
         <v>60.6</v>
@@ -6781,28 +6781,28 @@
         <v>113.8</v>
       </c>
       <c r="M67">
-        <v>10.265983</v>
+        <v>10.4239212</v>
       </c>
       <c r="N67">
-        <v>103.534017</v>
+        <v>103.3760788</v>
       </c>
       <c r="O67">
-        <v>25.88350425</v>
+        <v>25.8440197</v>
       </c>
       <c r="P67">
-        <v>77.65051274999999</v>
+        <v>77.5320591</v>
       </c>
       <c r="Q67">
-        <v>84.95051274999999</v>
+        <v>84.8320591</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2268402342917228</v>
+        <v>0.2316086337901878</v>
       </c>
       <c r="T67">
-        <v>2.634355999760993</v>
+        <v>2.703742022581739</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>11.08515375488153</v>
+        <v>10.91719687980757</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1043879354886638</v>
+        <v>0.1041292889752247</v>
       </c>
       <c r="C68">
-        <v>119.10528998603</v>
+        <v>116.3144350334103</v>
       </c>
       <c r="D68">
-        <v>259.73928998603</v>
+        <v>259.9974350334103</v>
       </c>
       <c r="E68">
-        <v>185.434</v>
+        <v>188.483</v>
       </c>
       <c r="F68">
-        <v>201.234</v>
+        <v>204.283</v>
       </c>
       <c r="G68">
         <v>60.6</v>
@@ -6863,28 +6863,28 @@
         <v>113.8</v>
       </c>
       <c r="M68">
-        <v>10.4239212</v>
+        <v>10.5818594</v>
       </c>
       <c r="N68">
-        <v>103.3760788</v>
+        <v>103.2181406</v>
       </c>
       <c r="O68">
-        <v>25.8440197</v>
+        <v>25.80453515</v>
       </c>
       <c r="P68">
-        <v>77.5320591</v>
+        <v>77.41360545000001</v>
       </c>
       <c r="Q68">
-        <v>84.8320591</v>
+        <v>84.71360545</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2316086337901878</v>
+        <v>0.2366660271976508</v>
       </c>
       <c r="T68">
-        <v>2.703742022581739</v>
+        <v>2.777333258906773</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>10.91719687980757</v>
+        <v>10.75425364279552</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1041292889752247</v>
+        <v>0.1038706424617856</v>
       </c>
       <c r="C69">
-        <v>116.3144350334103</v>
+        <v>113.5240937124497</v>
       </c>
       <c r="D69">
-        <v>259.9974350334103</v>
+        <v>260.2560937124497</v>
       </c>
       <c r="E69">
-        <v>188.483</v>
+        <v>191.532</v>
       </c>
       <c r="F69">
-        <v>204.283</v>
+        <v>207.3320000000001</v>
       </c>
       <c r="G69">
         <v>60.6</v>
@@ -6945,28 +6945,28 @@
         <v>113.8</v>
       </c>
       <c r="M69">
-        <v>10.5818594</v>
+        <v>10.7397976</v>
       </c>
       <c r="N69">
-        <v>103.2181406</v>
+        <v>103.0602024</v>
       </c>
       <c r="O69">
-        <v>25.80453515</v>
+        <v>25.7650506</v>
       </c>
       <c r="P69">
-        <v>77.41360545000001</v>
+        <v>77.2951518</v>
       </c>
       <c r="Q69">
-        <v>84.71360545</v>
+        <v>84.5951518</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2366660271976508</v>
+        <v>0.2420395076930801</v>
       </c>
       <c r="T69">
-        <v>2.777333258906773</v>
+        <v>2.855523947502121</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>10.75425364279552</v>
+        <v>10.59610285393088</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1038706424617856</v>
+        <v>0.1036119959483465</v>
       </c>
       <c r="C70">
-        <v>113.5240937124497</v>
+        <v>110.7342675576356</v>
       </c>
       <c r="D70">
-        <v>260.2560937124497</v>
+        <v>260.5152675576356</v>
       </c>
       <c r="E70">
-        <v>191.532</v>
+        <v>194.581</v>
       </c>
       <c r="F70">
-        <v>207.3320000000001</v>
+        <v>210.381</v>
       </c>
       <c r="G70">
         <v>60.6</v>
@@ -7027,28 +7027,28 @@
         <v>113.8</v>
       </c>
       <c r="M70">
-        <v>10.7397976</v>
+        <v>10.8977358</v>
       </c>
       <c r="N70">
-        <v>103.0602024</v>
+        <v>102.9022642</v>
       </c>
       <c r="O70">
-        <v>25.7650506</v>
+        <v>25.72556605</v>
       </c>
       <c r="P70">
-        <v>77.2951518</v>
+        <v>77.17669814999999</v>
       </c>
       <c r="Q70">
-        <v>84.5951518</v>
+        <v>84.47669814999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2420395076930801</v>
+        <v>0.2477596643495049</v>
       </c>
       <c r="T70">
-        <v>2.855523947502121</v>
+        <v>2.938759196652008</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>10.59610285393088</v>
+        <v>10.44253614590289</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1036119959483465</v>
+        <v>0.1033533494349074</v>
       </c>
       <c r="C71">
-        <v>110.7342675576356</v>
+        <v>107.9449581095737</v>
       </c>
       <c r="D71">
-        <v>260.5152675576356</v>
+        <v>260.7749581095737</v>
       </c>
       <c r="E71">
-        <v>194.581</v>
+        <v>197.63</v>
       </c>
       <c r="F71">
-        <v>210.381</v>
+        <v>213.43</v>
       </c>
       <c r="G71">
         <v>60.6</v>
@@ -7109,28 +7109,28 @@
         <v>113.8</v>
       </c>
       <c r="M71">
-        <v>10.8977358</v>
+        <v>11.055674</v>
       </c>
       <c r="N71">
-        <v>102.9022642</v>
+        <v>102.744326</v>
       </c>
       <c r="O71">
-        <v>25.72556605</v>
+        <v>25.6860815</v>
       </c>
       <c r="P71">
-        <v>77.17669814999999</v>
+        <v>77.0582445</v>
       </c>
       <c r="Q71">
-        <v>84.47669814999999</v>
+        <v>84.3582445</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2477596643495049</v>
+        <v>0.2538611647830247</v>
       </c>
       <c r="T71">
-        <v>2.938759196652008</v>
+        <v>3.027543462411888</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>10.44253614590289</v>
+        <v>10.29335705810428</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1033533494349074</v>
+        <v>0.1030947029214683</v>
       </c>
       <c r="C72">
-        <v>107.9449581095737</v>
+        <v>105.1561669150188</v>
       </c>
       <c r="D72">
-        <v>260.7749581095737</v>
+        <v>261.0351669150189</v>
       </c>
       <c r="E72">
-        <v>197.63</v>
+        <v>200.679</v>
       </c>
       <c r="F72">
-        <v>213.43</v>
+        <v>216.479</v>
       </c>
       <c r="G72">
         <v>60.6</v>
@@ -7191,28 +7191,28 @@
         <v>113.8</v>
       </c>
       <c r="M72">
-        <v>11.055674</v>
+        <v>11.2136122</v>
       </c>
       <c r="N72">
-        <v>102.744326</v>
+        <v>102.5863878</v>
       </c>
       <c r="O72">
-        <v>25.6860815</v>
+        <v>25.64659695</v>
       </c>
       <c r="P72">
-        <v>77.0582445</v>
+        <v>76.93979084999999</v>
       </c>
       <c r="Q72">
-        <v>84.3582445</v>
+        <v>84.23979084999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2538611647830247</v>
+        <v>0.2603834583498907</v>
       </c>
       <c r="T72">
-        <v>3.027543462411888</v>
+        <v>3.122450780982794</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>10.29335705810428</v>
+        <v>10.14838019813098</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1030947029214683</v>
+        <v>0.1028360564080292</v>
       </c>
       <c r="C73">
-        <v>105.1561669150189</v>
+        <v>102.3678955269058</v>
       </c>
       <c r="D73">
-        <v>261.0351669150189</v>
+        <v>261.2958955269058</v>
       </c>
       <c r="E73">
-        <v>200.679</v>
+        <v>203.728</v>
       </c>
       <c r="F73">
-        <v>216.479</v>
+        <v>219.528</v>
       </c>
       <c r="G73">
         <v>60.6</v>
@@ -7273,28 +7273,28 @@
         <v>113.8</v>
       </c>
       <c r="M73">
-        <v>11.2136122</v>
+        <v>11.3715504</v>
       </c>
       <c r="N73">
-        <v>102.5863878</v>
+        <v>102.4284496</v>
       </c>
       <c r="O73">
-        <v>25.64659695</v>
+        <v>25.6071124</v>
       </c>
       <c r="P73">
-        <v>76.93979084999999</v>
+        <v>76.82133719999999</v>
       </c>
       <c r="Q73">
-        <v>84.23979084999999</v>
+        <v>84.12133719999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2603834583498907</v>
+        <v>0.2673716300286756</v>
       </c>
       <c r="T73">
-        <v>3.122450780982793</v>
+        <v>3.224137193737334</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>10.14838019813098</v>
+        <v>10.00743047315694</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1028360564080292</v>
+        <v>0.1025774098945901</v>
       </c>
       <c r="C74">
-        <v>102.3678955269058</v>
+        <v>99.58014550437989</v>
       </c>
       <c r="D74">
-        <v>261.2958955269058</v>
+        <v>261.5571455043799</v>
       </c>
       <c r="E74">
-        <v>203.728</v>
+        <v>206.777</v>
       </c>
       <c r="F74">
-        <v>219.528</v>
+        <v>222.577</v>
       </c>
       <c r="G74">
         <v>60.6</v>
@@ -7355,28 +7355,28 @@
         <v>113.8</v>
       </c>
       <c r="M74">
-        <v>11.3715504</v>
+        <v>11.5294886</v>
       </c>
       <c r="N74">
-        <v>102.4284496</v>
+        <v>102.2705114</v>
       </c>
       <c r="O74">
-        <v>25.6071124</v>
+        <v>25.56762785</v>
       </c>
       <c r="P74">
-        <v>76.82133719999999</v>
+        <v>76.70288355</v>
       </c>
       <c r="Q74">
-        <v>84.12133719999999</v>
+        <v>84.00288354999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2673716300286756</v>
+        <v>0.2748774440540372</v>
       </c>
       <c r="T74">
-        <v>3.224137193737334</v>
+        <v>3.333355933362582</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>10.00743047315694</v>
+        <v>9.870342384483559</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1025774098945901</v>
+        <v>0.1032622633811509</v>
       </c>
       <c r="C75">
-        <v>99.58014550437989</v>
+        <v>95.84053514863325</v>
       </c>
       <c r="D75">
-        <v>261.5571455043799</v>
+        <v>260.8665351486333</v>
       </c>
       <c r="E75">
-        <v>206.777</v>
+        <v>209.826</v>
       </c>
       <c r="F75">
-        <v>222.577</v>
+        <v>225.626</v>
       </c>
       <c r="G75">
         <v>60.6</v>
@@ -7437,45 +7437,45 @@
         <v>113.8</v>
       </c>
       <c r="M75">
-        <v>11.5294886</v>
+        <v>12.070991</v>
       </c>
       <c r="N75">
-        <v>102.2705114</v>
+        <v>101.729009</v>
       </c>
       <c r="O75">
-        <v>25.56762785</v>
+        <v>25.43225225</v>
       </c>
       <c r="P75">
-        <v>76.70288355</v>
+        <v>76.29675674999999</v>
       </c>
       <c r="Q75">
-        <v>84.00288354999999</v>
+        <v>83.59675674999998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2748774440540372</v>
+        <v>0.2829606283890421</v>
       </c>
       <c r="T75">
-        <v>3.333355933362582</v>
+        <v>3.450976114497465</v>
       </c>
       <c r="U75">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>9.870342384483559</v>
+        <v>9.427560670039433</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1032622633811509</v>
+        <v>0.1030163668677118</v>
       </c>
       <c r="C76">
-        <v>95.84053514863325</v>
+        <v>93.03907862501399</v>
       </c>
       <c r="D76">
-        <v>260.8665351486333</v>
+        <v>261.114078625014</v>
       </c>
       <c r="E76">
-        <v>209.826</v>
+        <v>212.875</v>
       </c>
       <c r="F76">
-        <v>225.626</v>
+        <v>228.675</v>
       </c>
       <c r="G76">
         <v>60.6</v>
@@ -7519,28 +7519,28 @@
         <v>113.8</v>
       </c>
       <c r="M76">
-        <v>12.070991</v>
+        <v>12.2341125</v>
       </c>
       <c r="N76">
-        <v>101.729009</v>
+        <v>101.5658875</v>
       </c>
       <c r="O76">
-        <v>25.43225225</v>
+        <v>25.391471875</v>
       </c>
       <c r="P76">
-        <v>76.29675674999999</v>
+        <v>76.17441562499999</v>
       </c>
       <c r="Q76">
-        <v>83.59675674999998</v>
+        <v>83.47441562499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2829606283890421</v>
+        <v>0.2916904674708473</v>
       </c>
       <c r="T76">
-        <v>3.450976114497465</v>
+        <v>3.578005910123139</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>9.427560670039433</v>
+        <v>9.301859861105576</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1030163668677118</v>
+        <v>0.1027704703542727</v>
       </c>
       <c r="C77">
-        <v>93.03907862501399</v>
+        <v>90.23809234934012</v>
       </c>
       <c r="D77">
-        <v>261.114078625014</v>
+        <v>261.3620923493401</v>
       </c>
       <c r="E77">
-        <v>212.875</v>
+        <v>215.924</v>
       </c>
       <c r="F77">
-        <v>228.675</v>
+        <v>231.724</v>
       </c>
       <c r="G77">
         <v>60.6</v>
@@ -7601,28 +7601,28 @@
         <v>113.8</v>
       </c>
       <c r="M77">
-        <v>12.2341125</v>
+        <v>12.397234</v>
       </c>
       <c r="N77">
-        <v>101.5658875</v>
+        <v>101.402766</v>
       </c>
       <c r="O77">
-        <v>25.391471875</v>
+        <v>25.3506915</v>
       </c>
       <c r="P77">
-        <v>76.17441562499999</v>
+        <v>76.0520745</v>
       </c>
       <c r="Q77">
-        <v>83.47441562499999</v>
+        <v>83.3520745</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2916904674708473</v>
+        <v>0.301147793142803</v>
       </c>
       <c r="T77">
-        <v>3.578005910123139</v>
+        <v>3.715621522050952</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>9.301859861105576</v>
+        <v>9.179466968196293</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1027704703542727</v>
+        <v>0.1025245738408336</v>
       </c>
       <c r="C78">
-        <v>90.23809234934012</v>
+        <v>87.43757766285114</v>
       </c>
       <c r="D78">
-        <v>261.3620923493401</v>
+        <v>261.6105776628511</v>
       </c>
       <c r="E78">
-        <v>215.924</v>
+        <v>218.973</v>
       </c>
       <c r="F78">
-        <v>231.724</v>
+        <v>234.773</v>
       </c>
       <c r="G78">
         <v>60.6</v>
@@ -7683,28 +7683,28 @@
         <v>113.8</v>
       </c>
       <c r="M78">
-        <v>12.397234</v>
+        <v>12.5603555</v>
       </c>
       <c r="N78">
-        <v>101.402766</v>
+        <v>101.2396445</v>
       </c>
       <c r="O78">
-        <v>25.3506915</v>
+        <v>25.309911125</v>
       </c>
       <c r="P78">
-        <v>76.0520745</v>
+        <v>75.929733375</v>
       </c>
       <c r="Q78">
-        <v>83.3520745</v>
+        <v>83.229733375</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.301147793142803</v>
+        <v>0.3114274949601462</v>
       </c>
       <c r="T78">
-        <v>3.715621522050952</v>
+        <v>3.86520370892901</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>9.179466968196293</v>
+        <v>9.060253111466469</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1025245738408336</v>
+        <v>0.1022786773273945</v>
       </c>
       <c r="C79">
-        <v>87.43757766285114</v>
+        <v>84.63753591189189</v>
       </c>
       <c r="D79">
-        <v>261.6105776628511</v>
+        <v>261.8595359118919</v>
       </c>
       <c r="E79">
-        <v>218.973</v>
+        <v>222.022</v>
       </c>
       <c r="F79">
-        <v>234.773</v>
+        <v>237.822</v>
       </c>
       <c r="G79">
         <v>60.6</v>
@@ -7765,28 +7765,28 @@
         <v>113.8</v>
       </c>
       <c r="M79">
-        <v>12.5603555</v>
+        <v>12.723477</v>
       </c>
       <c r="N79">
-        <v>101.2396445</v>
+        <v>101.076523</v>
       </c>
       <c r="O79">
-        <v>25.309911125</v>
+        <v>25.26913075</v>
       </c>
       <c r="P79">
-        <v>75.929733375</v>
+        <v>75.80739224999999</v>
       </c>
       <c r="Q79">
-        <v>83.229733375</v>
+        <v>83.10739224999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3114274949601462</v>
+        <v>0.3226417151245204</v>
       </c>
       <c r="T79">
-        <v>3.86520370892901</v>
+        <v>4.028384276432345</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>9.060253111466469</v>
+        <v>8.944096020293824</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1022786773273945</v>
+        <v>0.1020327808139554</v>
       </c>
       <c r="C80">
-        <v>84.63753591189189</v>
+        <v>81.83796844793704</v>
       </c>
       <c r="D80">
-        <v>261.8595359118919</v>
+        <v>262.1089684479371</v>
       </c>
       <c r="E80">
-        <v>222.022</v>
+        <v>225.071</v>
       </c>
       <c r="F80">
-        <v>237.822</v>
+        <v>240.871</v>
       </c>
       <c r="G80">
         <v>60.6</v>
@@ -7847,28 +7847,28 @@
         <v>113.8</v>
       </c>
       <c r="M80">
-        <v>12.723477</v>
+        <v>12.8865985</v>
       </c>
       <c r="N80">
-        <v>101.076523</v>
+        <v>100.9134015</v>
       </c>
       <c r="O80">
-        <v>25.26913075</v>
+        <v>25.228350375</v>
       </c>
       <c r="P80">
-        <v>75.80739224999999</v>
+        <v>75.685051125</v>
       </c>
       <c r="Q80">
-        <v>83.10739224999999</v>
+        <v>82.985051125</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3226417151245204</v>
+        <v>0.3349239562569304</v>
       </c>
       <c r="T80">
-        <v>4.028384276432345</v>
+        <v>4.207105850364571</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>8.944096020293824</v>
+        <v>8.830879614973647</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1020327808139554</v>
+        <v>0.1017868843005163</v>
       </c>
       <c r="C81">
-        <v>81.83796844793704</v>
+        <v>79.03887662761551</v>
       </c>
       <c r="D81">
-        <v>262.1089684479371</v>
+        <v>262.3588766276155</v>
       </c>
       <c r="E81">
-        <v>225.071</v>
+        <v>228.12</v>
       </c>
       <c r="F81">
-        <v>240.871</v>
+        <v>243.92</v>
       </c>
       <c r="G81">
         <v>60.6</v>
@@ -7929,28 +7929,28 @@
         <v>113.8</v>
       </c>
       <c r="M81">
-        <v>12.8865985</v>
+        <v>13.04972</v>
       </c>
       <c r="N81">
-        <v>100.9134015</v>
+        <v>100.75028</v>
       </c>
       <c r="O81">
-        <v>25.228350375</v>
+        <v>25.18757</v>
       </c>
       <c r="P81">
-        <v>75.685051125</v>
+        <v>75.56271</v>
       </c>
       <c r="Q81">
-        <v>82.985051125</v>
+        <v>82.86270999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3349239562569304</v>
+        <v>0.3484344215025814</v>
       </c>
       <c r="T81">
-        <v>4.207105850364571</v>
+        <v>4.403699581690018</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>8.830879614973647</v>
+        <v>8.720493619786476</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1017868843005163</v>
+        <v>0.1015409877870772</v>
       </c>
       <c r="C82">
-        <v>79.03887662761551</v>
+        <v>76.24026181273496</v>
       </c>
       <c r="D82">
-        <v>262.3588766276155</v>
+        <v>262.609261812735</v>
       </c>
       <c r="E82">
-        <v>228.12</v>
+        <v>231.169</v>
       </c>
       <c r="F82">
-        <v>243.92</v>
+        <v>246.9690000000001</v>
       </c>
       <c r="G82">
         <v>60.6</v>
@@ -8011,28 +8011,28 @@
         <v>113.8</v>
       </c>
       <c r="M82">
-        <v>13.04972</v>
+        <v>13.2128415</v>
       </c>
       <c r="N82">
-        <v>100.75028</v>
+        <v>100.5871585</v>
       </c>
       <c r="O82">
-        <v>25.18757</v>
+        <v>25.146789625</v>
       </c>
       <c r="P82">
-        <v>75.56271</v>
+        <v>75.44036887499999</v>
       </c>
       <c r="Q82">
-        <v>82.86270999999999</v>
+        <v>82.74036887499999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3484344215025814</v>
+        <v>0.3633670409846167</v>
       </c>
       <c r="T82">
-        <v>4.403699581690018</v>
+        <v>4.620987389997092</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>8.720493619786476</v>
+        <v>8.612833204727384</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1015409877870772</v>
+        <v>0.101295091273638</v>
       </c>
       <c r="C83">
-        <v>76.24026181273496</v>
+        <v>73.44212537030691</v>
       </c>
       <c r="D83">
-        <v>262.609261812735</v>
+        <v>262.8601253703069</v>
       </c>
       <c r="E83">
-        <v>231.169</v>
+        <v>234.218</v>
       </c>
       <c r="F83">
-        <v>246.9690000000001</v>
+        <v>250.0180000000001</v>
       </c>
       <c r="G83">
         <v>60.6</v>
@@ -8093,28 +8093,28 @@
         <v>113.8</v>
       </c>
       <c r="M83">
-        <v>13.2128415</v>
+        <v>13.375963</v>
       </c>
       <c r="N83">
-        <v>100.5871585</v>
+        <v>100.424037</v>
       </c>
       <c r="O83">
-        <v>25.146789625</v>
+        <v>25.10600925</v>
       </c>
       <c r="P83">
-        <v>75.44036887499999</v>
+        <v>75.31802775</v>
       </c>
       <c r="Q83">
-        <v>82.74036887499999</v>
+        <v>82.61802775</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3633670409846167</v>
+        <v>0.3799588404091003</v>
       </c>
       <c r="T83">
-        <v>4.620987389997092</v>
+        <v>4.862418288116062</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>8.612833204727384</v>
+        <v>8.507798653450221</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.101295091273638</v>
+        <v>0.1010491947601989</v>
       </c>
       <c r="C84">
-        <v>73.44212537030691</v>
+        <v>70.64446867257107</v>
       </c>
       <c r="D84">
-        <v>262.8601253703069</v>
+        <v>263.1114686725711</v>
       </c>
       <c r="E84">
-        <v>234.218</v>
+        <v>237.2670000000001</v>
       </c>
       <c r="F84">
-        <v>250.0180000000001</v>
+        <v>253.0670000000001</v>
       </c>
       <c r="G84">
         <v>60.6</v>
@@ -8175,28 +8175,28 @@
         <v>113.8</v>
       </c>
       <c r="M84">
-        <v>13.375963</v>
+        <v>13.5390845</v>
       </c>
       <c r="N84">
-        <v>100.424037</v>
+        <v>100.2609155</v>
       </c>
       <c r="O84">
-        <v>25.10600925</v>
+        <v>25.065228875</v>
       </c>
       <c r="P84">
-        <v>75.31802775</v>
+        <v>75.19568662499999</v>
       </c>
       <c r="Q84">
-        <v>82.61802775</v>
+        <v>82.49568662499999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3799588404091003</v>
+        <v>0.3985026162364645</v>
       </c>
       <c r="T84">
-        <v>4.862418288116062</v>
+        <v>5.132252821307854</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>8.507798653450221</v>
+        <v>8.40529505521588</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1010491947601989</v>
+        <v>0.1008032982467598</v>
       </c>
       <c r="C85">
-        <v>70.64446867257107</v>
+        <v>67.84729309702095</v>
       </c>
       <c r="D85">
-        <v>263.1114686725711</v>
+        <v>263.363293097021</v>
       </c>
       <c r="E85">
-        <v>237.2670000000001</v>
+        <v>240.316</v>
       </c>
       <c r="F85">
-        <v>253.0670000000001</v>
+        <v>256.116</v>
       </c>
       <c r="G85">
         <v>60.6</v>
@@ -8257,28 +8257,28 @@
         <v>113.8</v>
       </c>
       <c r="M85">
-        <v>13.5390845</v>
+        <v>13.702206</v>
       </c>
       <c r="N85">
-        <v>100.2609155</v>
+        <v>100.097794</v>
       </c>
       <c r="O85">
-        <v>25.065228875</v>
+        <v>25.0244485</v>
       </c>
       <c r="P85">
-        <v>75.19568662499999</v>
+        <v>75.07334549999999</v>
       </c>
       <c r="Q85">
-        <v>82.49568662499999</v>
+        <v>82.37334549999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3985026162364645</v>
+        <v>0.4193643640422491</v>
       </c>
       <c r="T85">
-        <v>5.132252821307854</v>
+        <v>5.435816671148618</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>8.40529505521588</v>
+        <v>8.305232018844263</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1008032982467598</v>
+        <v>0.1005574017333207</v>
       </c>
       <c r="C86">
-        <v>67.84729309702095</v>
+        <v>65.05060002642836</v>
       </c>
       <c r="D86">
-        <v>263.363293097021</v>
+        <v>263.6156000264284</v>
       </c>
       <c r="E86">
-        <v>240.316</v>
+        <v>243.365</v>
       </c>
       <c r="F86">
-        <v>256.116</v>
+        <v>259.165</v>
       </c>
       <c r="G86">
         <v>60.6</v>
@@ -8339,28 +8339,28 @@
         <v>113.8</v>
       </c>
       <c r="M86">
-        <v>13.702206</v>
+        <v>13.8653275</v>
       </c>
       <c r="N86">
-        <v>100.097794</v>
+        <v>99.93467249999999</v>
       </c>
       <c r="O86">
-        <v>25.0244485</v>
+        <v>24.983668125</v>
       </c>
       <c r="P86">
-        <v>75.07334549999999</v>
+        <v>74.951004375</v>
       </c>
       <c r="Q86">
-        <v>82.37334549999999</v>
+        <v>82.25100437499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4193643640422487</v>
+        <v>0.443007678222138</v>
       </c>
       <c r="T86">
-        <v>5.435816671148614</v>
+        <v>5.779855700968148</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>8.305232018844263</v>
+        <v>8.20752340685786</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1005574017333207</v>
+        <v>0.1003115052198816</v>
       </c>
       <c r="C87">
-        <v>65.05060002642836</v>
+        <v>62.25439084886932</v>
       </c>
       <c r="D87">
-        <v>263.6156000264284</v>
+        <v>263.8683908488693</v>
       </c>
       <c r="E87">
-        <v>243.365</v>
+        <v>246.414</v>
       </c>
       <c r="F87">
-        <v>259.165</v>
+        <v>262.214</v>
       </c>
       <c r="G87">
         <v>60.6</v>
@@ -8421,28 +8421,28 @@
         <v>113.8</v>
       </c>
       <c r="M87">
-        <v>13.8653275</v>
+        <v>14.028449</v>
       </c>
       <c r="N87">
-        <v>99.93467249999999</v>
+        <v>99.771551</v>
       </c>
       <c r="O87">
-        <v>24.983668125</v>
+        <v>24.94288775</v>
       </c>
       <c r="P87">
-        <v>74.951004375</v>
+        <v>74.82866325000001</v>
       </c>
       <c r="Q87">
-        <v>82.25100437499999</v>
+        <v>82.12866325</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.443007678222138</v>
+        <v>0.4700286087134399</v>
       </c>
       <c r="T87">
-        <v>5.779855700968148</v>
+        <v>6.173043163619042</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.20752340685786</v>
+        <v>8.112087088173467</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1003115052198816</v>
+        <v>0.1000656087064425</v>
       </c>
       <c r="C88">
-        <v>62.25439084886932</v>
+        <v>59.45866695774907</v>
       </c>
       <c r="D88">
-        <v>263.8683908488693</v>
+        <v>264.1216669577491</v>
       </c>
       <c r="E88">
-        <v>246.414</v>
+        <v>249.463</v>
       </c>
       <c r="F88">
-        <v>262.214</v>
+        <v>265.263</v>
       </c>
       <c r="G88">
         <v>60.6</v>
@@ -8503,28 +8503,28 @@
         <v>113.8</v>
       </c>
       <c r="M88">
-        <v>14.028449</v>
+        <v>14.1915705</v>
       </c>
       <c r="N88">
-        <v>99.771551</v>
+        <v>99.6084295</v>
       </c>
       <c r="O88">
-        <v>24.94288775</v>
+        <v>24.902107375</v>
       </c>
       <c r="P88">
-        <v>74.82866325000001</v>
+        <v>74.706322125</v>
       </c>
       <c r="Q88">
-        <v>82.12866325</v>
+        <v>82.006322125</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4700286087134399</v>
+        <v>0.5012066054341727</v>
       </c>
       <c r="T88">
-        <v>6.173043163619042</v>
+        <v>6.626721005139304</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>8.112087088173467</v>
+        <v>8.018844707849635</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1000656087064425</v>
+        <v>0.09981971219300337</v>
       </c>
       <c r="C89">
-        <v>59.45866695774907</v>
+        <v>56.66342975182823</v>
       </c>
       <c r="D89">
-        <v>264.1216669577491</v>
+        <v>264.3754297518282</v>
       </c>
       <c r="E89">
-        <v>249.463</v>
+        <v>252.512</v>
       </c>
       <c r="F89">
-        <v>265.263</v>
+        <v>268.312</v>
       </c>
       <c r="G89">
         <v>60.6</v>
@@ -8585,28 +8585,28 @@
         <v>113.8</v>
       </c>
       <c r="M89">
-        <v>14.1915705</v>
+        <v>14.354692</v>
       </c>
       <c r="N89">
-        <v>99.6084295</v>
+        <v>99.445308</v>
       </c>
       <c r="O89">
-        <v>24.902107375</v>
+        <v>24.861327</v>
       </c>
       <c r="P89">
-        <v>74.706322125</v>
+        <v>74.58398099999999</v>
       </c>
       <c r="Q89">
-        <v>82.006322125</v>
+        <v>81.88398099999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5012066054341727</v>
+        <v>0.5375809349416947</v>
       </c>
       <c r="T89">
-        <v>6.626721005139304</v>
+        <v>7.156011820246278</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>8.018844707849635</v>
+        <v>7.927721472533162</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09981971219300337</v>
+        <v>0.09957381567956423</v>
       </c>
       <c r="C90">
-        <v>56.66342975182823</v>
+        <v>53.86868063524787</v>
       </c>
       <c r="D90">
-        <v>264.3754297518282</v>
+        <v>264.6296806352479</v>
       </c>
       <c r="E90">
-        <v>252.512</v>
+        <v>255.561</v>
       </c>
       <c r="F90">
-        <v>268.312</v>
+        <v>271.361</v>
       </c>
       <c r="G90">
         <v>60.6</v>
@@ -8667,28 +8667,28 @@
         <v>113.8</v>
       </c>
       <c r="M90">
-        <v>14.354692</v>
+        <v>14.5178135</v>
       </c>
       <c r="N90">
-        <v>99.445308</v>
+        <v>99.28218649999999</v>
       </c>
       <c r="O90">
-        <v>24.861327</v>
+        <v>24.820546625</v>
       </c>
       <c r="P90">
-        <v>74.58398099999999</v>
+        <v>74.461639875</v>
       </c>
       <c r="Q90">
-        <v>81.88398099999999</v>
+        <v>81.761639875</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5375809349416947</v>
+        <v>0.5805687789051295</v>
       </c>
       <c r="T90">
-        <v>7.156011820246278</v>
+        <v>7.781537329009065</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>7.927721472533162</v>
+        <v>7.838645950369866</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09957381567956423</v>
+        <v>0.09932791916612513</v>
       </c>
       <c r="C91">
-        <v>53.86868063524787</v>
+        <v>51.07442101755584</v>
       </c>
       <c r="D91">
-        <v>264.6296806352479</v>
+        <v>264.8844210175558</v>
       </c>
       <c r="E91">
-        <v>255.561</v>
+        <v>258.61</v>
       </c>
       <c r="F91">
-        <v>271.361</v>
+        <v>274.41</v>
       </c>
       <c r="G91">
         <v>60.6</v>
@@ -8749,28 +8749,28 @@
         <v>113.8</v>
       </c>
       <c r="M91">
-        <v>14.5178135</v>
+        <v>14.680935</v>
       </c>
       <c r="N91">
-        <v>99.28218649999999</v>
+        <v>99.11906499999999</v>
       </c>
       <c r="O91">
-        <v>24.820546625</v>
+        <v>24.77976625</v>
       </c>
       <c r="P91">
-        <v>74.461639875</v>
+        <v>74.33929875</v>
       </c>
       <c r="Q91">
-        <v>81.761639875</v>
+        <v>81.63929874999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5805687789051295</v>
+        <v>0.6321541916612515</v>
       </c>
       <c r="T91">
-        <v>7.781537329009065</v>
+        <v>8.532167939524411</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>7.838645950369866</v>
+        <v>7.751549884254646</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09932791916612513</v>
+        <v>0.09908202265268601</v>
       </c>
       <c r="C92">
-        <v>51.07442101755584</v>
+        <v>48.28065231373267</v>
       </c>
       <c r="D92">
-        <v>264.8844210175558</v>
+        <v>265.1396523137327</v>
       </c>
       <c r="E92">
-        <v>258.61</v>
+        <v>261.659</v>
       </c>
       <c r="F92">
-        <v>274.41</v>
+        <v>277.4590000000001</v>
       </c>
       <c r="G92">
         <v>60.6</v>
@@ -8831,28 +8831,28 @@
         <v>113.8</v>
       </c>
       <c r="M92">
-        <v>14.680935</v>
+        <v>14.8440565</v>
       </c>
       <c r="N92">
-        <v>99.11906499999999</v>
+        <v>98.95594349999999</v>
       </c>
       <c r="O92">
-        <v>24.77976625</v>
+        <v>24.738985875</v>
       </c>
       <c r="P92">
-        <v>74.33929875</v>
+        <v>74.21695762499999</v>
       </c>
       <c r="Q92">
-        <v>81.63929874999999</v>
+        <v>81.51695762499999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6321541916612515</v>
+        <v>0.6952030294742892</v>
       </c>
       <c r="T92">
-        <v>8.532167939524411</v>
+        <v>9.449605352376498</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>7.751549884254646</v>
+        <v>7.666368017394705</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09908202265268601</v>
+        <v>0.0993881261392469</v>
       </c>
       <c r="C93">
-        <v>48.28065231373267</v>
+        <v>44.91400332164989</v>
       </c>
       <c r="D93">
-        <v>265.1396523137327</v>
+        <v>264.8220033216499</v>
       </c>
       <c r="E93">
-        <v>261.659</v>
+        <v>264.708</v>
       </c>
       <c r="F93">
-        <v>277.4590000000001</v>
+        <v>280.508</v>
       </c>
       <c r="G93">
         <v>60.6</v>
@@ -8913,45 +8913,45 @@
         <v>113.8</v>
       </c>
       <c r="M93">
-        <v>14.8440565</v>
+        <v>15.2315844</v>
       </c>
       <c r="N93">
-        <v>98.95594349999999</v>
+        <v>98.56841559999999</v>
       </c>
       <c r="O93">
-        <v>24.738985875</v>
+        <v>24.6421039</v>
       </c>
       <c r="P93">
-        <v>74.21695762499999</v>
+        <v>73.9263117</v>
       </c>
       <c r="Q93">
-        <v>81.51695762499999</v>
+        <v>81.2263117</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6952030294742892</v>
+        <v>0.7740140767405866</v>
       </c>
       <c r="T93">
-        <v>9.449605352376498</v>
+        <v>10.59640211844161</v>
       </c>
       <c r="U93">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V93">
         <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y93">
-        <v>7.666368017394705</v>
+        <v>7.471317297759252</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0993881261392469</v>
+        <v>0.09914822962580778</v>
       </c>
       <c r="C94">
-        <v>44.91400332164989</v>
+        <v>42.11388360057799</v>
       </c>
       <c r="D94">
-        <v>264.8220033216499</v>
+        <v>265.070883600578</v>
       </c>
       <c r="E94">
-        <v>264.708</v>
+        <v>267.7570000000001</v>
       </c>
       <c r="F94">
-        <v>280.508</v>
+        <v>283.5570000000001</v>
       </c>
       <c r="G94">
         <v>60.6</v>
@@ -8995,28 +8995,28 @@
         <v>113.8</v>
       </c>
       <c r="M94">
-        <v>15.2315844</v>
+        <v>15.3971451</v>
       </c>
       <c r="N94">
-        <v>98.56841559999999</v>
+        <v>98.40285489999999</v>
       </c>
       <c r="O94">
-        <v>24.6421039</v>
+        <v>24.600713725</v>
       </c>
       <c r="P94">
-        <v>73.9263117</v>
+        <v>73.802141175</v>
       </c>
       <c r="Q94">
-        <v>81.2263117</v>
+        <v>81.102141175</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7740140767405866</v>
+        <v>0.875342566082969</v>
       </c>
       <c r="T94">
-        <v>10.59640211844161</v>
+        <v>12.07085510338247</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>7.471317297759252</v>
+        <v>7.390980552622055</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09914822962580778</v>
+        <v>0.09890833311236868</v>
       </c>
       <c r="C95">
-        <v>42.11388360057799</v>
+        <v>39.31423211598104</v>
       </c>
       <c r="D95">
-        <v>265.070883600578</v>
+        <v>265.3202321159811</v>
       </c>
       <c r="E95">
-        <v>267.7570000000001</v>
+        <v>270.806</v>
       </c>
       <c r="F95">
-        <v>283.5570000000001</v>
+        <v>286.6060000000001</v>
       </c>
       <c r="G95">
         <v>60.6</v>
@@ -9077,28 +9077,28 @@
         <v>113.8</v>
       </c>
       <c r="M95">
-        <v>15.3971451</v>
+        <v>15.5627058</v>
       </c>
       <c r="N95">
-        <v>98.40285489999999</v>
+        <v>98.23729419999999</v>
       </c>
       <c r="O95">
-        <v>24.600713725</v>
+        <v>24.55932355</v>
       </c>
       <c r="P95">
-        <v>73.802141175</v>
+        <v>73.67797064999999</v>
       </c>
       <c r="Q95">
-        <v>81.102141175</v>
+        <v>80.97797064999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.875342566082969</v>
+        <v>1.010447218539479</v>
       </c>
       <c r="T95">
-        <v>12.07085510338247</v>
+        <v>14.03679241663694</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>7.390980552622055</v>
+        <v>7.312353099934587</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09890833311236868</v>
+        <v>0.09866843659892957</v>
       </c>
       <c r="C96">
-        <v>39.31423211598104</v>
+        <v>36.51505019049392</v>
       </c>
       <c r="D96">
-        <v>265.3202321159811</v>
+        <v>265.5700501904939</v>
       </c>
       <c r="E96">
-        <v>270.806</v>
+        <v>273.855</v>
       </c>
       <c r="F96">
-        <v>286.6060000000001</v>
+        <v>289.655</v>
       </c>
       <c r="G96">
         <v>60.6</v>
@@ -9159,28 +9159,28 @@
         <v>113.8</v>
       </c>
       <c r="M96">
-        <v>15.5627058</v>
+        <v>15.7282665</v>
       </c>
       <c r="N96">
-        <v>98.23729419999999</v>
+        <v>98.07173349999999</v>
       </c>
       <c r="O96">
-        <v>24.55932355</v>
+        <v>24.517933375</v>
       </c>
       <c r="P96">
-        <v>73.67797064999999</v>
+        <v>73.553800125</v>
       </c>
       <c r="Q96">
-        <v>80.97797064999999</v>
+        <v>80.85380012499999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.010447218539479</v>
+        <v>1.199593731978593</v>
       </c>
       <c r="T96">
-        <v>14.03679241663694</v>
+        <v>16.78910465519321</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>7.312353099934587</v>
+        <v>7.235380962040539</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09866843659892957</v>
+        <v>0.09842854008549046</v>
       </c>
       <c r="C97">
-        <v>36.51505019049392</v>
+        <v>33.71633915173749</v>
       </c>
       <c r="D97">
-        <v>265.5700501904939</v>
+        <v>265.8203391517375</v>
       </c>
       <c r="E97">
-        <v>273.855</v>
+        <v>276.9040000000001</v>
       </c>
       <c r="F97">
-        <v>289.655</v>
+        <v>292.7040000000001</v>
       </c>
       <c r="G97">
         <v>60.6</v>
@@ -9241,28 +9241,28 @@
         <v>113.8</v>
       </c>
       <c r="M97">
-        <v>15.7282665</v>
+        <v>15.8938272</v>
       </c>
       <c r="N97">
-        <v>98.07173349999999</v>
+        <v>97.90617279999999</v>
       </c>
       <c r="O97">
-        <v>24.517933375</v>
+        <v>24.4765432</v>
       </c>
       <c r="P97">
-        <v>73.553800125</v>
+        <v>73.4296296</v>
       </c>
       <c r="Q97">
-        <v>80.85380012499999</v>
+        <v>80.7296296</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.199593731978593</v>
+        <v>1.483313502137264</v>
       </c>
       <c r="T97">
-        <v>16.78910465519321</v>
+        <v>20.91757301302762</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>7.235380962040539</v>
+        <v>7.160012410352616</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09842854008549046</v>
+        <v>0.09818864357205134</v>
       </c>
       <c r="C98">
-        <v>33.71633915173754</v>
+        <v>30.91810033234265</v>
       </c>
       <c r="D98">
-        <v>265.8203391517375</v>
+        <v>266.0711003323427</v>
       </c>
       <c r="E98">
-        <v>276.904</v>
+        <v>279.953</v>
       </c>
       <c r="F98">
-        <v>292.704</v>
+        <v>295.753</v>
       </c>
       <c r="G98">
         <v>60.6</v>
@@ -9323,28 +9323,28 @@
         <v>113.8</v>
       </c>
       <c r="M98">
-        <v>15.8938272</v>
+        <v>16.0593879</v>
       </c>
       <c r="N98">
-        <v>97.90617279999999</v>
+        <v>97.74061209999999</v>
       </c>
       <c r="O98">
-        <v>24.4765432</v>
+        <v>24.435153025</v>
       </c>
       <c r="P98">
-        <v>73.4296296</v>
+        <v>73.30545907499999</v>
       </c>
       <c r="Q98">
-        <v>80.7296296</v>
+        <v>80.60545907499998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.48331350213726</v>
+        <v>1.956179785735043</v>
       </c>
       <c r="T98">
-        <v>20.91757301302757</v>
+        <v>27.79835360941821</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>7.160012410352618</v>
+        <v>7.086197849421145</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09818864357205134</v>
+        <v>0.09794874705861223</v>
       </c>
       <c r="C99">
-        <v>30.91810033234265</v>
+        <v>28.12033506997335</v>
       </c>
       <c r="D99">
-        <v>266.0711003323427</v>
+        <v>266.3223350699733</v>
       </c>
       <c r="E99">
-        <v>279.953</v>
+        <v>283.002</v>
       </c>
       <c r="F99">
-        <v>295.753</v>
+        <v>298.802</v>
       </c>
       <c r="G99">
         <v>60.6</v>
@@ -9405,28 +9405,28 @@
         <v>113.8</v>
       </c>
       <c r="M99">
-        <v>16.0593879</v>
+        <v>16.2249486</v>
       </c>
       <c r="N99">
-        <v>97.74061209999999</v>
+        <v>97.57505139999999</v>
       </c>
       <c r="O99">
-        <v>24.435153025</v>
+        <v>24.39376285</v>
       </c>
       <c r="P99">
-        <v>73.30545907499999</v>
+        <v>73.18128854999999</v>
       </c>
       <c r="Q99">
-        <v>80.60545907499998</v>
+        <v>80.48128854999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.956179785735043</v>
+        <v>2.901912352930609</v>
       </c>
       <c r="T99">
-        <v>27.79835360941821</v>
+        <v>41.55991480219951</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>7.086197849421145</v>
+        <v>7.013889708100523</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09794874705861223</v>
+        <v>0.09770885054517311</v>
       </c>
       <c r="C100">
-        <v>28.12033506997335</v>
+        <v>25.32304470735039</v>
       </c>
       <c r="D100">
-        <v>266.3223350699733</v>
+        <v>266.5740447073504</v>
       </c>
       <c r="E100">
-        <v>283.002</v>
+        <v>286.051</v>
       </c>
       <c r="F100">
-        <v>298.802</v>
+        <v>301.8510000000001</v>
       </c>
       <c r="G100">
         <v>60.6</v>
@@ -9487,28 +9487,28 @@
         <v>113.8</v>
       </c>
       <c r="M100">
-        <v>16.2249486</v>
+        <v>16.39050930000001</v>
       </c>
       <c r="N100">
-        <v>97.57505139999999</v>
+        <v>97.40949069999999</v>
       </c>
       <c r="O100">
-        <v>24.39376285</v>
+        <v>24.352372675</v>
       </c>
       <c r="P100">
-        <v>73.18128854999999</v>
+        <v>73.05711802499999</v>
       </c>
       <c r="Q100">
-        <v>80.48128854999999</v>
+        <v>80.35711802499999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.901912352930609</v>
+        <v>5.739110054517306</v>
       </c>
       <c r="T100">
-        <v>41.55991480219951</v>
+        <v>82.84459838054339</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>7.013889708100523</v>
+        <v>6.943042337311627</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09770885054517311</v>
-      </c>
-      <c r="C101">
-        <v>25.32304470735039</v>
-      </c>
-      <c r="D101">
-        <v>266.5740447073504</v>
-      </c>
-      <c r="E101">
-        <v>286.051</v>
-      </c>
-      <c r="F101">
-        <v>301.8510000000001</v>
-      </c>
-      <c r="G101">
-        <v>60.6</v>
-      </c>
-      <c r="H101">
-        <v>289.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>121.1</v>
-      </c>
-      <c r="K101">
-        <v>7.299999999999997</v>
-      </c>
-      <c r="L101">
-        <v>113.8</v>
-      </c>
-      <c r="M101">
-        <v>16.39050930000001</v>
-      </c>
-      <c r="N101">
-        <v>97.40949069999999</v>
-      </c>
-      <c r="O101">
-        <v>24.352372675</v>
-      </c>
-      <c r="P101">
-        <v>73.05711802499999</v>
-      </c>
-      <c r="Q101">
-        <v>80.35711802499999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.739110054517306</v>
-      </c>
-      <c r="T101">
-        <v>82.84459838054339</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.040725</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>6.943042337311627</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
